--- a/InputData/trans/BVS/BAU Vehicle Subsidy.xlsx
+++ b/InputData/trans/BVS/BAU Vehicle Subsidy.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\trans\BVS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\kjh_local\NEXTgroup_local\2025_local\2. EPS\업데이트 파일\eps-southkorea-3.3.1_2025update_v4.0.3\InputData\trans\BVS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B291C5C-0D68-4026-BF5B-12E51E7484B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B30BB3E-5F1B-424B-A5B7-389E64FDCCD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="843" firstSheet="7" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Passenger Vehicle Calculations" sheetId="114" r:id="rId2"/>
-    <sheet name="Commercial Vehicles" sheetId="117" r:id="rId3"/>
+    <sheet name="승합차 및 화물차" sheetId="118" r:id="rId3"/>
     <sheet name="psgr" sheetId="17" r:id="rId4"/>
     <sheet name="BVS-psgr-LDVs" sheetId="2" r:id="rId5"/>
     <sheet name="BVS-psgr-HDVs" sheetId="101" r:id="rId6"/>
     <sheet name="BVS-psgr-aircraft" sheetId="105" r:id="rId7"/>
-    <sheet name="BVP-psgr-rail" sheetId="104" r:id="rId8"/>
+    <sheet name="BVS-psgr-rail" sheetId="104" r:id="rId8"/>
     <sheet name="BVS-psgr-ships" sheetId="103" r:id="rId9"/>
     <sheet name="BVS-psgr-motorbikes" sheetId="102" r:id="rId10"/>
     <sheet name="frgt" sheetId="106" r:id="rId11"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="39">
   <si>
     <t>Sources:</t>
   </si>
@@ -78,108 +78,6 @@
     <t>BVS BAU Vehicle Subsidy</t>
   </si>
   <si>
-    <t>State EV Subsidy Amounts</t>
-  </si>
-  <si>
-    <t>This list only includes rebates on the EV itself, not on charging equipment.</t>
-  </si>
-  <si>
-    <t>It also omits states that do not offer a rebate but do exempt EVs from sales, use, or excise taxes.</t>
-  </si>
-  <si>
-    <t>State Rebates + Tax Credits Updated 8/11/2021</t>
-  </si>
-  <si>
-    <t>TC</t>
-  </si>
-  <si>
-    <t>https://www.energysage.com/electric-vehicles/costs-and-benefits-evs/ev-tax-credits/</t>
-  </si>
-  <si>
-    <t>Rebates</t>
-  </si>
-  <si>
-    <t>https://www.tesla.com/support/incentives</t>
-  </si>
-  <si>
-    <t>Note: Could be an optimistic estimate</t>
-  </si>
-  <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>Population, millions (June 2022)</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>CO</t>
-  </si>
-  <si>
-    <t>LDV</t>
-  </si>
-  <si>
-    <t>Note: average of cars and truck subsidies, which are different</t>
-  </si>
-  <si>
-    <t>CT</t>
-  </si>
-  <si>
-    <t>https://afdc.energy.gov/laws/11609</t>
-  </si>
-  <si>
-    <t>DE</t>
-  </si>
-  <si>
-    <t>NY</t>
-  </si>
-  <si>
-    <t>Subsidy goes up to 2000 based on battery</t>
-  </si>
-  <si>
-    <t>TX</t>
-  </si>
-  <si>
-    <t>Note: only 1 year program</t>
-  </si>
-  <si>
-    <t>CA</t>
-  </si>
-  <si>
-    <t>LA</t>
-  </si>
-  <si>
-    <t>ME</t>
-  </si>
-  <si>
-    <t>MD</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>NJ</t>
-  </si>
-  <si>
-    <t>OR</t>
-  </si>
-  <si>
-    <t>VT</t>
-  </si>
-  <si>
-    <t>Note: Up to 4000</t>
-  </si>
-  <si>
-    <t>Rest of country</t>
-  </si>
-  <si>
-    <t>USA</t>
-  </si>
-  <si>
-    <t>Note: Pennsylvania offers a $1750 rebate, but only to the first 250 qualified applicants.</t>
-  </si>
-  <si>
     <t>Total Tax Credit (2012$)</t>
   </si>
   <si>
@@ -189,146 +87,121 @@
     <t>plugin hybrid vehicles</t>
   </si>
   <si>
-    <t>Pop-Weighted State Avg Tax Credit (2012$)</t>
+    <t>2025년 전기자동차 보급사업 보조금 업무처리지침(25.1.15)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>Federal EV Subsidy Amount (2012$)</t>
+    <t>연도별 전기차 혜택</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>2022 to 2012 $</t>
+    <t>생활법령정보</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>Federal IRA Incentives</t>
+    <t>전기차 보조금 정보</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>https://energyinnovation.org/publication/analyzing-the-impact-of-the-inflation-reduction-act-on-electric-vehicle-uptake-in-the-united-states/</t>
+    <t>2024 원/달려 환률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>ICCT and Energy Innovation</t>
+    <t>2024 to 2012 $</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>Methodology:</t>
+    <t>https://www.exchange-rates.org/ko/exchange-rate-history/usd-krw-2024</t>
   </si>
   <si>
-    <t>Calculations:</t>
+    <t>2024년도 평균치</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>2022 $ to 2012 $</t>
+    <t>※ 하이브리드자동차에 대한 구매보조금제도는 2021년 1월 1일 폐지되었습니다. 다만, 세금 감면 혜택은 유지됩니다. 하이브리드자동차에 대한 세금 감면에 대한 자세한 내용은 이 사이트 『환경친화적 자동차』: &lt;하이브리드자동차 – 하이브리드 자동차 구입 – 하이브리드자동차 세금감면&gt; 에서 확인할 수 있습니다.</t>
   </si>
   <si>
-    <t>Fraction of buses owned by private entities (see trans/FoVObE)</t>
+    <t>* 2026년 부터는 2025년도와 동일한 값을 넣음</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>The credit caps are $7,500 for vehicles under 14,000 lbs and $40,000 for vehicles over 14,000 lbs (class 4 and above). We need to calculate</t>
+    <t>https://www.amazoncar.co.kr/single/reservation?type=electric_car</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>a weighted average credit for our freight LDV category, which includes vehicle classes 2b-6.</t>
+    <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?csmSeq=1404&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>AEO classifications (see AEO table footnotes)</t>
+    <t>battery electric vehicles</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>Class</t>
+    <t>* 기준: 국고+지자체(서울) 최대값</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>Weight</t>
+    <t>EV Subsidy Amount (단위: 만원)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>Commercial light trucks</t>
+    <t>https://ev.or.kr/nportal/buySupprt/initSubsidyPaymentCheckAction.do</t>
   </si>
   <si>
-    <t>2b</t>
+    <t>무공해차 통합누리집</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>8,501-10,000 lbs</t>
+    <t>Psgr-HDVs</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>Light Medium trucks</t>
+    <t>frgt-LDVs</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>10,001-14,000 lbs</t>
+    <t>frgt-HDVS</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>Medium trucks</t>
+    <t>단위: 만원</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>14,001-26,000 lbs</t>
+    <t>전기- 대형 승객용 차량</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>Weighted Average calculated relative to AEO sales</t>
+    <t>수소 - 승합</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>Sales (thousands)</t>
+    <t xml:space="preserve">전기차 차동별 보조금(국비+지방비(서울) 최대금액) </t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>Total Commercial Light Truck Sales</t>
+    <t>경형 화물차</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>Light Medium Subtotal</t>
-  </si>
-  <si>
-    <t>Medium Subtotal</t>
-  </si>
-  <si>
-    <t>Weighted Average Credit</t>
-  </si>
-  <si>
-    <t>For commercial vehicle credits, we find that the credit caps of $7,500 for vehicles under 14,000 pounds or $40,000 for vehicles over 14,000 pounds apply in all years. We apply the credit to all new sales of commercial trucks, using a weighted average credit value for our freight LDV category which covers both light and medium duty trucks. We also apply the credit to a fraction of buses, excluding buses purchased by the government. The credit runs from 2023-2032.</t>
-  </si>
-  <si>
-    <t>Commercial Vehicle Credit (2022 $)</t>
-  </si>
-  <si>
-    <t>Passenger Vehicle Credit (2022 $)</t>
-  </si>
-  <si>
-    <t>Psgr HDV (2012 $)</t>
-  </si>
-  <si>
-    <t>Freight HDV (2012 $)</t>
-  </si>
-  <si>
-    <t>Psgr LDV (2012 $)</t>
-  </si>
-  <si>
-    <t>Credit Amount (2012 $)</t>
-  </si>
-  <si>
-    <t>Source: EIA AEO 2023, Tables 44 and 49</t>
-  </si>
-  <si>
-    <t>AEO 2023</t>
-  </si>
-  <si>
-    <t>values from original IRA analysis</t>
-  </si>
-  <si>
-    <t>Foreign Entities of Concern Multiplier</t>
-  </si>
-  <si>
-    <t>BloombergNEF, MarkLines, Department of Energy</t>
-  </si>
-  <si>
-    <t>We assume a 56% cut in our original analysis to represent FEOC restrictions for the year 2024, based on BNEF data. We assume more restrictive guidance starting in 2025 will reduce the credit amount by 75%.</t>
+    <t>소형 화물차</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="167" formatCode="m\-d"/>
+  <numFmts count="3">
+    <numFmt numFmtId="176" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -336,7 +209,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -364,94 +237,65 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -462,12 +306,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFE2F3"/>
-        <bgColor rgb="FFCFE2F3"/>
       </patternFill>
     </fill>
   </fills>
@@ -588,10 +426,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -601,54 +439,25 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="8" applyFill="1"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="6" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="38" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="6" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="30" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="30" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="30" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="31" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="31" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="31"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="31" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="8" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="31" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="31" applyFont="1"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="31" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="31" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="31" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="31" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="31" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="31" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="8" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="31" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="16" fillId="0" borderId="0" xfId="31" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="32" applyFont="1"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="31" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="33">
     <cellStyle name="Body: normal cell" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -668,8 +477,6 @@
     <cellStyle name="Header: bottom row 2" xfId="27" xr:uid="{1D7C7530-C012-4975-BABC-640C7522786E}"/>
     <cellStyle name="Header: bottom row 3" xfId="20" xr:uid="{D4A074B3-C733-4663-AFD1-0229ED226851}"/>
     <cellStyle name="Header: bottom row 4" xfId="12" xr:uid="{040BC27B-CB03-4FDE-8B80-4B13E048F2D8}"/>
-    <cellStyle name="Hyperlink" xfId="8" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Normal 3" xfId="23" xr:uid="{F75C00A9-4AB0-4B9A-85F1-1BA242EDAF83}"/>
     <cellStyle name="Normal 4" xfId="16" xr:uid="{D654EA3C-A2C4-4D73-9768-00B5086DE48E}"/>
@@ -679,11 +486,13 @@
     <cellStyle name="Parent row 2" xfId="28" xr:uid="{1C336998-EB49-46ED-B880-BDD7385C1A9F}"/>
     <cellStyle name="Parent row 3" xfId="21" xr:uid="{E39AA093-46A1-425E-9FAB-5E5D22915C9B}"/>
     <cellStyle name="Parent row 4" xfId="13" xr:uid="{766EEC84-3128-426E-8720-CF77BEFFA340}"/>
-    <cellStyle name="Percent" xfId="30" builtinId="5"/>
     <cellStyle name="Table title" xfId="7" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
     <cellStyle name="Table title 2" xfId="29" xr:uid="{75C5CFB8-5852-4F3E-A011-ECC9372E7F45}"/>
     <cellStyle name="Table title 3" xfId="22" xr:uid="{D3D003D1-845D-4DC8-878D-F5771072DB44}"/>
     <cellStyle name="Table title 4" xfId="14" xr:uid="{09C4790A-A5AC-4A4C-A2DC-60844BB56B28}"/>
+    <cellStyle name="백분율" xfId="30" builtinId="5"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="8" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -696,55 +505,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>474705</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>44451</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A770E37F-B482-C48F-69E5-AB265CCAA341}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="1841501"/>
-          <a:ext cx="6532605" cy="4648200"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1034,87 +794,117 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:C35"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="2" max="2" width="69.26953125" customWidth="1"/>
+    <col min="2" max="2" width="69.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B3" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="15"/>
+    </row>
+    <row r="4" spans="1:3">
       <c r="B4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="B5" s="3">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B7" s="4"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B8" s="20" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B9" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="B6" s="3"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="B9" s="3"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="B10" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="B11" s="16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="B12" s="3"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B14" s="4"/>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B26" s="3"/>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B28" s="4"/>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" s="1"/>
+    <row r="13" spans="1:3">
+      <c r="B13" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="B14" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="B15" s="4"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="B16" s="3"/>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="4"/>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" s="3"/>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" s="4"/>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{4581867B-9054-4731-B6D7-80BFD47F8B2E}"/>
+    <hyperlink ref="B11" r:id="rId2" xr:uid="{04F4B6B1-A408-49DF-9E50-1A2A047456D6}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3C5C6BF-BE7A-4625-8CB5-34C673B46C4E}">
-  <sheetPr>
+  <sheetPr codeName="Sheet10">
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -1209,7 +999,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1304,7 +1094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1399,7 +1189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1494,7 +1284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1589,7 +1379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1684,7 +1474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1779,7 +1569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1875,34 +1665,36 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{079976DC-F6C0-456E-8DA9-4BF43DDF1E10}">
-  <sheetPr>
+  <sheetPr codeName="Sheet11">
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <sheetData/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DB978D3-75FC-40E7-B55E-E0DE8CD249DB}">
-  <sheetPr>
+  <sheetPr codeName="Sheet12">
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AG8"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:33">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -1997,112 +1789,134 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:33">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <f>'Commercial Vehicles'!B11</f>
-        <v>10121.162702145082</v>
-      </c>
-      <c r="E2">
-        <f>'Commercial Vehicles'!C11</f>
-        <v>10059.772494365814</v>
-      </c>
-      <c r="F2">
-        <f>'Commercial Vehicles'!D11</f>
-        <v>10050.763799597085</v>
-      </c>
-      <c r="G2">
-        <f>'Commercial Vehicles'!E11</f>
-        <v>10127.428607069427</v>
-      </c>
-      <c r="H2">
-        <f>'Commercial Vehicles'!F11</f>
-        <v>10269.11524721545</v>
-      </c>
-      <c r="I2">
-        <f>'Commercial Vehicles'!G11</f>
-        <v>10350.781370900584</v>
-      </c>
-      <c r="J2">
-        <f>'Commercial Vehicles'!H11</f>
-        <v>10353.674088089921</v>
-      </c>
-      <c r="K2">
-        <f>'Commercial Vehicles'!I11</f>
-        <v>10294.239800360298</v>
-      </c>
-      <c r="L2">
-        <f>'Commercial Vehicles'!J11</f>
-        <v>10251.903689786537</v>
-      </c>
-      <c r="M2">
-        <f>'Commercial Vehicles'!K11</f>
-        <v>10279.777009851599</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="B2" s="17">
+        <f>'승합차 및 화물차'!C17</f>
+        <v>8859.1485340727922</v>
+      </c>
+      <c r="C2" s="17">
+        <f>'승합차 및 화물차'!D17</f>
+        <v>8053.7713946116301</v>
+      </c>
+      <c r="D2" s="17">
+        <f>'승합차 및 화물차'!E17</f>
+        <v>6765.1679714737684</v>
+      </c>
+      <c r="E2" s="17">
+        <f>'승합차 및 화물차'!F17</f>
+        <v>6190.6656119914733</v>
+      </c>
+      <c r="F2" s="17">
+        <f>'승합차 및 화물차'!G17</f>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="G2" s="17">
+        <f>'승합차 및 화물차'!H17</f>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="H2" s="17">
+        <f>'승합차 및 화물차'!I17</f>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="I2" s="17">
+        <f>'승합차 및 화물차'!J17</f>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="J2" s="17">
+        <f>'승합차 및 화물차'!K17</f>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="K2" s="17">
+        <f>'승합차 및 화물차'!L17</f>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="L2" s="17">
+        <f>'승합차 및 화물차'!M17</f>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="M2" s="17">
+        <f>'승합차 및 화물차'!N17</f>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="N2" s="17">
+        <f>'승합차 및 화물차'!O17</f>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="O2" s="17">
+        <f>'승합차 및 화물차'!P17</f>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="P2" s="17">
+        <f>'승합차 및 화물차'!Q17</f>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="Q2" s="17">
+        <f>'승합차 및 화물차'!R17</f>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="R2" s="17">
+        <f>'승합차 및 화물차'!S17</f>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="S2" s="17">
+        <f>'승합차 및 화물차'!T17</f>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="T2" s="17">
+        <f>'승합차 및 화물차'!U17</f>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="U2" s="17">
+        <f>'승합차 및 화물차'!V17</f>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="V2" s="17">
+        <f>'승합차 및 화물차'!W17</f>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="W2" s="17">
+        <f>'승합차 및 화물차'!X17</f>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="X2" s="17">
+        <f>'승합차 및 화물차'!Y17</f>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="Y2" s="17">
+        <f>'승합차 및 화물차'!Z17</f>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="Z2" s="17">
+        <f>'승합차 및 화물차'!AA17</f>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="AA2" s="17">
+        <f>'승합차 및 화물차'!AB17</f>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="AB2" s="17">
+        <f>'승합차 및 화물차'!AC17</f>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="AC2" s="17">
+        <f>'승합차 및 화물차'!AD17</f>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="AD2" s="17">
+        <f>'승합차 및 화물차'!AE17</f>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="AE2" s="17">
+        <f>'승합차 및 화물차'!AF17</f>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="AF2" s="17"/>
+      <c r="AG2" s="17"/>
+    </row>
+    <row r="3" spans="1:33">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2197,7 +2011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:33">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2292,7 +2106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:33">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -2387,7 +2201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:33">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2398,44 +2212,34 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <f>D2</f>
-        <v>10121.162702145082</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <f t="shared" ref="E6:M6" si="0">E2</f>
-        <v>10059.772494365814</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <f t="shared" si="0"/>
-        <v>10050.763799597085</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <f t="shared" si="0"/>
-        <v>10127.428607069427</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <f t="shared" si="0"/>
-        <v>10269.11524721545</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <f t="shared" si="0"/>
-        <v>10350.781370900584</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <f t="shared" si="0"/>
-        <v>10353.674088089921</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <f t="shared" si="0"/>
-        <v>10294.239800360298</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <f t="shared" si="0"/>
-        <v>10251.903689786537</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <f t="shared" si="0"/>
-        <v>10279.777009851599</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -2492,7 +2296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:33">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -2587,7 +2391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:33">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -2598,44 +2402,34 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <f>D2</f>
-        <v>10121.162702145082</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <f t="shared" ref="E8:M8" si="1">E2</f>
-        <v>10059.772494365814</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <f t="shared" si="1"/>
-        <v>10050.763799597085</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <f t="shared" si="1"/>
-        <v>10127.428607069427</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <f t="shared" si="1"/>
-        <v>10269.11524721545</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <f t="shared" si="1"/>
-        <v>10350.781370900584</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <f t="shared" si="1"/>
-        <v>10353.674088089921</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <f t="shared" si="1"/>
-        <v>10294.239800360298</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <f t="shared" si="1"/>
-        <v>10251.903689786537</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <f t="shared" si="1"/>
-        <v>10279.777009851599</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -2693,6 +2487,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -2700,16 +2495,16 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AF139E4-90E8-4DFC-ABC4-1799BB0C313F}">
-  <sheetPr>
+  <sheetPr codeName="Sheet13">
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -2804,112 +2599,132 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <f>'Commercial Vehicles'!$B$8</f>
-        <v>31400</v>
-      </c>
-      <c r="E2">
-        <f>'Commercial Vehicles'!$B$8</f>
-        <v>31400</v>
-      </c>
-      <c r="F2">
-        <f>'Commercial Vehicles'!$B$8</f>
-        <v>31400</v>
-      </c>
-      <c r="G2">
-        <f>'Commercial Vehicles'!$B$8</f>
-        <v>31400</v>
-      </c>
-      <c r="H2">
-        <f>'Commercial Vehicles'!$B$8</f>
-        <v>31400</v>
-      </c>
-      <c r="I2">
-        <f>'Commercial Vehicles'!$B$8</f>
-        <v>31400</v>
-      </c>
-      <c r="J2">
-        <f>'Commercial Vehicles'!$B$8</f>
-        <v>31400</v>
-      </c>
-      <c r="K2">
-        <f>'Commercial Vehicles'!$B$8</f>
-        <v>31400</v>
-      </c>
-      <c r="L2">
-        <f>'Commercial Vehicles'!$B$8</f>
-        <v>31400</v>
-      </c>
-      <c r="M2">
-        <f>'Commercial Vehicles'!$B$8</f>
-        <v>31400</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="B2" s="17">
+        <f>'승합차 및 화물차'!C18</f>
+        <v>16912.919928684423</v>
+      </c>
+      <c r="C2" s="17">
+        <f>'승합차 및 화물차'!D18</f>
+        <v>14110.207483359576</v>
+      </c>
+      <c r="D2" s="17">
+        <f>'승합차 및 화물차'!E18</f>
+        <v>10448.426089276154</v>
+      </c>
+      <c r="E2" s="17">
+        <f>'승합차 및 화물차'!F18</f>
+        <v>10856.483839936476</v>
+      </c>
+      <c r="F2" s="17">
+        <f>'승합차 및 화물차'!G18</f>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="G2" s="17">
+        <f>'승합차 및 화물차'!H18</f>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="H2" s="17">
+        <f>'승합차 및 화물차'!I18</f>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="I2" s="17">
+        <f>'승합차 및 화물차'!J18</f>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="J2" s="17">
+        <f>'승합차 및 화물차'!K18</f>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="K2" s="17">
+        <f>'승합차 및 화물차'!L18</f>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="L2" s="17">
+        <f>'승합차 및 화물차'!M18</f>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="M2" s="17">
+        <f>'승합차 및 화물차'!N18</f>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="N2" s="17">
+        <f>'승합차 및 화물차'!O18</f>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="O2" s="17">
+        <f>'승합차 및 화물차'!P18</f>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="P2" s="17">
+        <f>'승합차 및 화물차'!Q18</f>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="Q2" s="17">
+        <f>'승합차 및 화물차'!R18</f>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="R2" s="17">
+        <f>'승합차 및 화물차'!S18</f>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="S2" s="17">
+        <f>'승합차 및 화물차'!T18</f>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="T2" s="17">
+        <f>'승합차 및 화물차'!U18</f>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="U2" s="17">
+        <f>'승합차 및 화물차'!V18</f>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="V2" s="17">
+        <f>'승합차 및 화물차'!W18</f>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="W2" s="17">
+        <f>'승합차 및 화물차'!X18</f>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="X2" s="17">
+        <f>'승합차 및 화물차'!Y18</f>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="Y2" s="17">
+        <f>'승합차 및 화물차'!Z18</f>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="Z2" s="17">
+        <f>'승합차 및 화물차'!AA18</f>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="AA2" s="17">
+        <f>'승합차 및 화물차'!AB18</f>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="AB2" s="17">
+        <f>'승합차 및 화물차'!AC18</f>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="AC2" s="17">
+        <f>'승합차 및 화물차'!AD18</f>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="AD2" s="17">
+        <f>'승합차 및 화물차'!AE18</f>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="AE2" s="17">
+        <f>'승합차 및 화물차'!AF18</f>
+        <v>10684.670050184763</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3004,7 +2819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3099,7 +2914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3194,7 +3009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -3205,44 +3020,34 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <f>D2</f>
-        <v>31400</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <f t="shared" ref="E6:M6" si="0">E2</f>
-        <v>31400</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <f t="shared" si="0"/>
-        <v>31400</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <f t="shared" si="0"/>
-        <v>31400</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <f t="shared" si="0"/>
-        <v>31400</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <f t="shared" si="0"/>
-        <v>31400</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <f t="shared" si="0"/>
-        <v>31400</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <f t="shared" si="0"/>
-        <v>31400</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <f t="shared" si="0"/>
-        <v>31400</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <f t="shared" si="0"/>
-        <v>31400</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -3299,7 +3104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -3394,7 +3199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -3405,44 +3210,34 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <f>D2</f>
-        <v>31400</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <f t="shared" ref="E8:M8" si="1">E2</f>
-        <v>31400</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <f t="shared" si="1"/>
-        <v>31400</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <f t="shared" si="1"/>
-        <v>31400</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <f t="shared" si="1"/>
-        <v>31400</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <f t="shared" si="1"/>
-        <v>31400</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <f t="shared" si="1"/>
-        <v>31400</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <f t="shared" si="1"/>
-        <v>31400</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <f t="shared" si="1"/>
-        <v>31400</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <f t="shared" si="1"/>
-        <v>31400</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -3500,22 +3295,23 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1274E315-3F6B-4E92-87B5-9C3C1B4F85DA}">
-  <sheetPr>
+  <sheetPr codeName="Sheet14">
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -3610,7 +3406,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3705,7 +3501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3800,7 +3596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3895,7 +3691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3990,7 +3786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -4085,7 +3881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -4180,7 +3976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -4276,22 +4072,23 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C51E62EB-7B15-406D-A4C2-A4FF0C772B4A}">
-  <sheetPr>
+  <sheetPr codeName="Sheet15">
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -4386,7 +4183,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -4481,7 +4278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -4576,7 +4373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4671,7 +4468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -4766,7 +4563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -4861,7 +4658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -4956,7 +4753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -5052,22 +4849,23 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A44835A4-EB4E-4E1F-85F1-DB244E55CC6B}">
-  <sheetPr>
+  <sheetPr codeName="Sheet16">
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -5162,7 +4960,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -5257,7 +5055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -5352,7 +5150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -5447,7 +5245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -5542,7 +5340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -5637,7 +5435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -5732,7 +5530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -5828,22 +5626,23 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D2F53C0-8CAC-4671-B512-864662BE4DD4}">
-  <sheetPr>
+  <sheetPr codeName="Sheet17">
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -5938,7 +5737,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -6033,7 +5832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -6128,7 +5927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -6223,7 +6022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -6318,7 +6117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -6413,7 +6212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -6508,7 +6307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -6604,31 +6403,33 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD8A3CC6-8591-4A07-9E4B-1DE39D29E87F}">
-  <dimension ref="A1:AF59"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:AE28"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="45.453125" customWidth="1"/>
-    <col min="2" max="2" width="15.7265625" customWidth="1"/>
-    <col min="3" max="3" width="19.1796875" customWidth="1"/>
+    <col min="1" max="1" width="45.5" customWidth="1"/>
+    <col min="2" max="2" width="15.75" customWidth="1"/>
+    <col min="3" max="3" width="19.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31">
       <c r="B3">
         <v>2021</v>
       </c>
@@ -6720,4421 +6521,2467 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31">
       <c r="A4" s="5" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="B4">
-        <v>2435.88</v>
+        <v>1000</v>
       </c>
       <c r="C4">
-        <v>1697.08</v>
+        <v>900</v>
       </c>
       <c r="D4">
-        <f>D9*(1-0.56)</f>
-        <v>1795.2747999999999</v>
+        <v>860</v>
       </c>
       <c r="E4">
-        <f t="shared" ref="E4:M4" si="0">E9*(1-0.56)</f>
-        <v>1761.5091999999997</v>
+        <v>800</v>
       </c>
       <c r="F4">
-        <f>F9*(1-0.75)</f>
-        <v>1102.7774999999999</v>
+        <v>640</v>
       </c>
       <c r="G4">
-        <f t="shared" ref="G4:M4" si="1">G9*(1-0.75)</f>
-        <v>1057.2825</v>
+        <v>0</v>
       </c>
       <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31">
+      <c r="A5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>2250</v>
+      </c>
+      <c r="C6">
+        <v>3250</v>
+      </c>
+      <c r="D6">
+        <v>3250</v>
+      </c>
+      <c r="E6">
+        <v>3250</v>
+      </c>
+      <c r="F6">
+        <v>2950</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31">
+      <c r="A7" s="5"/>
+    </row>
+    <row r="8" spans="1:31">
+      <c r="A8" s="5"/>
+    </row>
+    <row r="9" spans="1:31">
+      <c r="A9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>1363.18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31">
+      <c r="A10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>0.73191600598044548</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31">
+      <c r="A11" s="5"/>
+    </row>
+    <row r="12" spans="1:31">
+      <c r="A12" s="5"/>
+    </row>
+    <row r="13" spans="1:31">
+      <c r="A13" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31">
+      <c r="B14">
+        <v>2021</v>
+      </c>
+      <c r="C14">
+        <v>2022</v>
+      </c>
+      <c r="D14">
+        <v>2023</v>
+      </c>
+      <c r="E14">
+        <v>2024</v>
+      </c>
+      <c r="F14">
+        <v>2025</v>
+      </c>
+      <c r="G14">
+        <v>2026</v>
+      </c>
+      <c r="H14">
+        <v>2027</v>
+      </c>
+      <c r="I14">
+        <v>2028</v>
+      </c>
+      <c r="J14">
+        <v>2029</v>
+      </c>
+      <c r="K14">
+        <v>2030</v>
+      </c>
+      <c r="L14">
+        <v>2031</v>
+      </c>
+      <c r="M14">
+        <v>2032</v>
+      </c>
+      <c r="N14">
+        <v>2033</v>
+      </c>
+      <c r="O14">
+        <v>2034</v>
+      </c>
+      <c r="P14">
+        <v>2035</v>
+      </c>
+      <c r="Q14">
+        <v>2036</v>
+      </c>
+      <c r="R14">
+        <v>2037</v>
+      </c>
+      <c r="S14">
+        <v>2038</v>
+      </c>
+      <c r="T14">
+        <v>2039</v>
+      </c>
+      <c r="U14">
+        <v>2040</v>
+      </c>
+      <c r="V14">
+        <v>2041</v>
+      </c>
+      <c r="W14">
+        <v>2042</v>
+      </c>
+      <c r="X14">
+        <v>2043</v>
+      </c>
+      <c r="Y14">
+        <v>2044</v>
+      </c>
+      <c r="Z14">
+        <v>2045</v>
+      </c>
+      <c r="AA14">
+        <v>2046</v>
+      </c>
+      <c r="AB14">
+        <v>2047</v>
+      </c>
+      <c r="AC14">
+        <v>2048</v>
+      </c>
+      <c r="AD14">
+        <v>2049</v>
+      </c>
+      <c r="AE14">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31">
+      <c r="A15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5">
+        <f>B4*10000/$B$9*$B$10</f>
+        <v>5369.1809297410864</v>
+      </c>
+      <c r="C15" s="5">
+        <f t="shared" ref="C15:AE17" si="0">C4*10000/$B$9*$B$10</f>
+        <v>4832.2628367669777</v>
+      </c>
+      <c r="D15" s="5">
+        <f t="shared" si="0"/>
+        <v>4617.4955995773344</v>
+      </c>
+      <c r="E15" s="5">
+        <f t="shared" si="0"/>
+        <v>4295.3447437928689</v>
+      </c>
+      <c r="F15" s="5">
+        <f t="shared" si="0"/>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="G15" s="5">
+        <f>$F$15</f>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="H15" s="5">
+        <f t="shared" ref="H15:AE15" si="1">$F$15</f>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="I15" s="5">
         <f t="shared" si="1"/>
-        <v>1022.79</v>
-      </c>
-      <c r="I4">
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="J15" s="5">
         <f t="shared" si="1"/>
-        <v>1024.8150000000001</v>
-      </c>
-      <c r="J4">
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="K15" s="5">
         <f t="shared" si="1"/>
-        <v>1031.5474999999999</v>
-      </c>
-      <c r="K4">
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="L15" s="5">
         <f t="shared" si="1"/>
-        <v>1089.8074999999999</v>
-      </c>
-      <c r="L4">
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="M15" s="5">
         <f t="shared" si="1"/>
-        <v>1145.5925</v>
-      </c>
-      <c r="M4">
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="N15" s="5">
         <f t="shared" si="1"/>
-        <v>1156.375</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5">
-        <v>6652.72</v>
-      </c>
-      <c r="C5">
-        <v>3617.05</v>
-      </c>
-      <c r="D5">
-        <f>D10*(1-0.56)</f>
-        <v>1795.2747999999999</v>
-      </c>
-      <c r="E5">
-        <f t="shared" ref="E5:M5" si="2">E10*(1-0.56)</f>
-        <v>1761.5091999999997</v>
-      </c>
-      <c r="F5">
-        <f>F10*(1-0.75)</f>
-        <v>1102.7774999999999</v>
-      </c>
-      <c r="G5">
-        <f t="shared" ref="G5:M5" si="3">G10*(1-0.75)</f>
-        <v>1057.2825</v>
-      </c>
-      <c r="H5">
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="O15" s="5">
+        <f t="shared" si="1"/>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="P15" s="5">
+        <f t="shared" si="1"/>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="Q15" s="5">
+        <f t="shared" si="1"/>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="R15" s="5">
+        <f t="shared" si="1"/>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="S15" s="5">
+        <f t="shared" si="1"/>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="T15" s="5">
+        <f t="shared" si="1"/>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="U15" s="5">
+        <f t="shared" si="1"/>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="V15" s="5">
+        <f t="shared" si="1"/>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="W15" s="5">
+        <f t="shared" si="1"/>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="X15" s="5">
+        <f t="shared" si="1"/>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="Y15" s="5">
+        <f t="shared" si="1"/>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="Z15" s="5">
+        <f t="shared" si="1"/>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="AA15" s="5">
+        <f t="shared" si="1"/>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="AB15" s="5">
+        <f t="shared" si="1"/>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="AC15" s="5">
+        <f t="shared" si="1"/>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="AD15" s="5">
+        <f t="shared" si="1"/>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="AE15" s="5">
+        <f t="shared" si="1"/>
+        <v>3436.2757950342957</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31">
+      <c r="A16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5">
+        <f t="shared" ref="B16:Q17" si="2">B5*10000/$B$9*$B$10</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AB16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="5">
+        <f t="shared" si="2"/>
+        <v>12080.657091917445</v>
+      </c>
+      <c r="C17" s="5">
+        <f t="shared" si="0"/>
+        <v>17449.838021658532</v>
+      </c>
+      <c r="D17" s="5">
+        <f t="shared" si="0"/>
+        <v>17449.838021658532</v>
+      </c>
+      <c r="E17" s="5">
+        <f t="shared" si="0"/>
+        <v>17449.838021658532</v>
+      </c>
+      <c r="F17" s="5">
+        <f t="shared" si="0"/>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="G17" s="5">
+        <f>$F$17</f>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="H17" s="5">
+        <f t="shared" ref="H17:AE17" si="3">$F$17</f>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="I17" s="5">
         <f t="shared" si="3"/>
-        <v>1022.79</v>
-      </c>
-      <c r="I5">
+        <v>15839.083742736204</v>
+      </c>
+      <c r="J17" s="5">
         <f t="shared" si="3"/>
-        <v>1024.8150000000001</v>
-      </c>
-      <c r="J5">
+        <v>15839.083742736204</v>
+      </c>
+      <c r="K17" s="5">
         <f t="shared" si="3"/>
-        <v>1031.5474999999999</v>
-      </c>
-      <c r="K5">
+        <v>15839.083742736204</v>
+      </c>
+      <c r="L17" s="5">
         <f t="shared" si="3"/>
-        <v>1089.8074999999999</v>
-      </c>
-      <c r="L5">
+        <v>15839.083742736204</v>
+      </c>
+      <c r="M17" s="5">
         <f t="shared" si="3"/>
-        <v>1145.5925</v>
-      </c>
-      <c r="M5">
+        <v>15839.083742736204</v>
+      </c>
+      <c r="N17" s="5">
         <f t="shared" si="3"/>
-        <v>1156.375</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A6" s="5"/>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="B8">
-        <v>2021</v>
-      </c>
-      <c r="C8">
-        <v>2022</v>
-      </c>
-      <c r="D8">
-        <v>2023</v>
-      </c>
-      <c r="E8">
-        <v>2024</v>
-      </c>
-      <c r="F8">
-        <v>2025</v>
-      </c>
-      <c r="G8">
-        <v>2026</v>
-      </c>
-      <c r="H8">
-        <v>2027</v>
-      </c>
-      <c r="I8">
-        <v>2028</v>
-      </c>
-      <c r="J8">
-        <v>2029</v>
-      </c>
-      <c r="K8">
-        <v>2030</v>
-      </c>
-      <c r="L8">
-        <v>2031</v>
-      </c>
-      <c r="M8">
-        <v>2032</v>
-      </c>
-      <c r="N8">
-        <v>2033</v>
-      </c>
-      <c r="O8">
-        <v>2034</v>
-      </c>
-      <c r="P8">
-        <v>2035</v>
-      </c>
-      <c r="Q8">
-        <v>2036</v>
-      </c>
-      <c r="R8">
-        <v>2037</v>
-      </c>
-      <c r="S8">
-        <v>2038</v>
-      </c>
-      <c r="T8">
-        <v>2039</v>
-      </c>
-      <c r="U8">
-        <v>2040</v>
-      </c>
-      <c r="V8">
-        <v>2041</v>
-      </c>
-      <c r="W8">
-        <v>2042</v>
-      </c>
-      <c r="X8">
-        <v>2043</v>
-      </c>
-      <c r="Y8">
-        <v>2044</v>
-      </c>
-      <c r="Z8">
-        <v>2045</v>
-      </c>
-      <c r="AA8">
-        <v>2046</v>
-      </c>
-      <c r="AB8">
-        <v>2047</v>
-      </c>
-      <c r="AC8">
-        <v>2048</v>
-      </c>
-      <c r="AD8">
-        <v>2049</v>
-      </c>
-      <c r="AE8">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9">
-        <v>2435.88</v>
-      </c>
-      <c r="C9">
-        <v>1697.08</v>
-      </c>
-      <c r="D9">
-        <v>4080.17</v>
-      </c>
-      <c r="E9">
-        <v>4003.43</v>
-      </c>
-      <c r="F9">
-        <v>4411.1099999999997</v>
-      </c>
-      <c r="G9">
-        <v>4229.13</v>
-      </c>
-      <c r="H9">
-        <v>4091.16</v>
-      </c>
-      <c r="I9">
-        <v>4099.26</v>
-      </c>
-      <c r="J9">
-        <v>4126.1899999999996</v>
-      </c>
-      <c r="K9">
-        <v>4359.2299999999996</v>
-      </c>
-      <c r="L9">
-        <v>4582.37</v>
-      </c>
-      <c r="M9">
-        <v>4625.5</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <v>0</v>
-      </c>
-      <c r="Y9">
-        <v>0</v>
-      </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0</v>
-      </c>
-      <c r="AC9">
-        <v>0</v>
-      </c>
-      <c r="AD9">
-        <v>0</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10">
-        <v>6652.72</v>
-      </c>
-      <c r="C10">
-        <v>3617.05</v>
-      </c>
-      <c r="D10">
-        <v>4080.17</v>
-      </c>
-      <c r="E10">
-        <v>4003.43</v>
-      </c>
-      <c r="F10">
-        <v>4411.1099999999997</v>
-      </c>
-      <c r="G10">
-        <v>4229.13</v>
-      </c>
-      <c r="H10">
-        <v>4091.16</v>
-      </c>
-      <c r="I10">
-        <v>4099.26</v>
-      </c>
-      <c r="J10">
-        <v>4126.1899999999996</v>
-      </c>
-      <c r="K10">
-        <v>4359.2299999999996</v>
-      </c>
-      <c r="L10">
-        <v>4582.37</v>
-      </c>
-      <c r="M10">
-        <v>4625.5</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <v>0</v>
-      </c>
-      <c r="Y10">
-        <v>0</v>
-      </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <v>0</v>
-      </c>
-      <c r="AC10">
-        <v>0</v>
-      </c>
-      <c r="AD10">
-        <v>0</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A11" s="5"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A12" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A13" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A14" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A15" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="7"/>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A17" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A18" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="8"/>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="8" t="s">
+        <v>15839.083742736204</v>
+      </c>
+      <c r="O17" s="5">
+        <f t="shared" si="3"/>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="P17" s="5">
+        <f t="shared" si="3"/>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="Q17" s="5">
+        <f t="shared" si="3"/>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="R17" s="5">
+        <f t="shared" si="3"/>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="S17" s="5">
+        <f t="shared" si="3"/>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="T17" s="5">
+        <f t="shared" si="3"/>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="U17" s="5">
+        <f t="shared" si="3"/>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="V17" s="5">
+        <f t="shared" si="3"/>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="W17" s="5">
+        <f t="shared" si="3"/>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="X17" s="5">
+        <f t="shared" si="3"/>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="Y17" s="5">
+        <f t="shared" si="3"/>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="Z17" s="5">
+        <f t="shared" si="3"/>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="AA17" s="5">
+        <f t="shared" si="3"/>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="AB17" s="5">
+        <f t="shared" si="3"/>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="AC17" s="5">
+        <f t="shared" si="3"/>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="AD17" s="5">
+        <f t="shared" si="3"/>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="AE17" s="5">
+        <f t="shared" si="3"/>
+        <v>15839.083742736204</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31">
+      <c r="G18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" ht="102">
+      <c r="A21" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="8">
-        <v>2020</v>
-      </c>
-      <c r="E19" s="8">
-        <f t="shared" ref="E19:J19" si="4">D19+1</f>
-        <v>2021</v>
-      </c>
-      <c r="F19" s="8">
-        <f t="shared" si="4"/>
-        <v>2022</v>
-      </c>
-      <c r="G19" s="8">
-        <f t="shared" si="4"/>
-        <v>2023</v>
-      </c>
-      <c r="H19" s="8">
-        <f t="shared" si="4"/>
-        <v>2024</v>
-      </c>
-      <c r="I19" s="8">
-        <f t="shared" si="4"/>
-        <v>2025</v>
-      </c>
-      <c r="J19" s="8">
-        <f t="shared" si="4"/>
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="8">
-        <v>5.6849999999999996</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="8">
-        <v>4750</v>
-      </c>
-      <c r="E20" s="8">
-        <v>4750</v>
-      </c>
-      <c r="F20" s="8">
-        <v>3000</v>
-      </c>
-      <c r="G20" s="8">
-        <v>3000</v>
-      </c>
-      <c r="H20" s="8">
-        <v>2400</v>
-      </c>
-      <c r="I20" s="8">
-        <v>2400</v>
-      </c>
-      <c r="J20" s="8">
-        <v>2400</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="8">
-        <v>3.5710000000000002</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="8">
-        <v>2250</v>
-      </c>
-      <c r="E21" s="8">
-        <v>2250</v>
-      </c>
-      <c r="F21" s="8">
-        <v>2250</v>
-      </c>
-      <c r="G21" s="8">
-        <v>2250</v>
-      </c>
-      <c r="H21" s="8">
-        <v>2250</v>
-      </c>
-      <c r="I21" s="8">
-        <v>2250</v>
-      </c>
-      <c r="J21" s="8">
-        <v>2250</v>
-      </c>
-      <c r="K21" s="8"/>
-      <c r="R21" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A22" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="8">
-        <v>0.96799999999999997</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="8">
-        <v>2500</v>
-      </c>
-      <c r="E22" s="8">
-        <v>2500</v>
-      </c>
-      <c r="F22" s="8">
-        <v>2500</v>
-      </c>
-      <c r="G22" s="8">
-        <v>2500</v>
-      </c>
-      <c r="H22" s="8">
-        <v>2500</v>
-      </c>
-      <c r="I22" s="8">
-        <v>2500</v>
-      </c>
-      <c r="J22" s="8">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="8">
-        <v>8.3800000000000008</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D23" s="11">
-        <v>2000</v>
-      </c>
-      <c r="E23" s="11">
-        <v>2000</v>
-      </c>
-      <c r="F23" s="11">
-        <v>2000</v>
-      </c>
-      <c r="G23" s="11">
-        <v>2000</v>
-      </c>
-      <c r="H23" s="11">
-        <v>2000</v>
-      </c>
-      <c r="I23" s="11">
-        <v>2000</v>
-      </c>
-      <c r="J23" s="11">
-        <v>2000</v>
-      </c>
-      <c r="K23" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="L23" s="10"/>
-      <c r="M23" s="12"/>
-    </row>
-    <row r="24" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="8">
-        <v>28.64</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D24" s="8">
-        <v>2500</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0</v>
-      </c>
-      <c r="F24" s="8">
-        <v>0</v>
-      </c>
-      <c r="G24" s="8">
-        <v>0</v>
-      </c>
-      <c r="H24" s="8">
-        <v>0</v>
-      </c>
-      <c r="I24" s="8">
-        <v>0</v>
-      </c>
-      <c r="J24" s="8">
-        <v>0</v>
-      </c>
-      <c r="K24" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="R24" s="13"/>
-    </row>
-    <row r="25" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="8">
-        <v>39.35</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D25" s="8">
-        <v>2500</v>
-      </c>
-      <c r="E25" s="8">
-        <v>2500</v>
-      </c>
-      <c r="F25" s="8">
-        <v>2500</v>
-      </c>
-      <c r="G25" s="8">
-        <v>2500</v>
-      </c>
-      <c r="H25" s="8">
-        <v>2500</v>
-      </c>
-      <c r="I25" s="8">
-        <v>2500</v>
-      </c>
-      <c r="J25" s="8">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="8">
-        <v>4.665</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26" s="14">
-        <v>1500</v>
-      </c>
-      <c r="E26" s="14">
-        <v>1500</v>
-      </c>
-      <c r="F26" s="14">
-        <v>1500</v>
-      </c>
-      <c r="G26" s="14">
-        <v>1500</v>
-      </c>
-      <c r="H26" s="14">
-        <v>1500</v>
-      </c>
-      <c r="I26" s="14">
-        <v>1500</v>
-      </c>
-      <c r="J26" s="14">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="8">
-        <v>1.341</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D27" s="8">
-        <v>2000</v>
-      </c>
-      <c r="E27" s="8">
-        <v>2000</v>
-      </c>
-      <c r="F27" s="8">
-        <v>2000</v>
-      </c>
-      <c r="G27" s="8">
-        <v>2000</v>
-      </c>
-      <c r="H27" s="8">
-        <v>2000</v>
-      </c>
-      <c r="I27" s="8">
-        <v>2000</v>
-      </c>
-      <c r="J27" s="8">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="8">
-        <v>6.0380000000000003</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D28" s="8">
-        <v>2500</v>
-      </c>
-      <c r="E28" s="8">
-        <v>2500</v>
-      </c>
-      <c r="F28" s="8">
-        <v>2500</v>
-      </c>
-      <c r="G28" s="8">
-        <v>2500</v>
-      </c>
-      <c r="H28" s="8">
-        <v>2500</v>
-      </c>
-      <c r="I28" s="8">
-        <v>2500</v>
-      </c>
-      <c r="J28" s="8">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="8">
-        <v>6.8730000000000002</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D29" s="8">
-        <v>2500</v>
-      </c>
-      <c r="E29" s="8">
-        <v>2500</v>
-      </c>
-      <c r="F29" s="8">
-        <v>2500</v>
-      </c>
-      <c r="G29" s="8">
-        <v>2500</v>
-      </c>
-      <c r="H29" s="8">
-        <v>2500</v>
-      </c>
-      <c r="I29" s="8">
-        <v>2500</v>
-      </c>
-      <c r="J29" s="8">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="8">
-        <v>8.8849999999999998</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D30" s="8">
-        <v>5000</v>
-      </c>
-      <c r="E30" s="8">
-        <v>5000</v>
-      </c>
-      <c r="F30" s="8">
-        <v>5000</v>
-      </c>
-      <c r="G30" s="8">
-        <v>5000</v>
-      </c>
-      <c r="H30" s="8">
-        <v>5000</v>
-      </c>
-      <c r="I30" s="8">
-        <v>5000</v>
-      </c>
-      <c r="J30" s="8">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="8">
-        <v>4.1760000000000002</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D31" s="8">
-        <v>2500</v>
-      </c>
-      <c r="E31" s="8">
-        <v>2500</v>
-      </c>
-      <c r="F31" s="8">
-        <v>2500</v>
-      </c>
-      <c r="G31" s="8">
-        <v>2500</v>
-      </c>
-      <c r="H31" s="8">
-        <v>2500</v>
-      </c>
-      <c r="I31" s="8">
-        <v>2500</v>
-      </c>
-      <c r="J31" s="8">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="8">
-        <v>0.624</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D32" s="8">
-        <v>4000</v>
-      </c>
-      <c r="E32" s="8">
-        <v>4000</v>
-      </c>
-      <c r="F32" s="8">
-        <v>4000</v>
-      </c>
-      <c r="G32" s="8">
-        <v>4000</v>
-      </c>
-      <c r="H32" s="8">
-        <v>4000</v>
-      </c>
-      <c r="I32" s="8">
-        <v>4000</v>
-      </c>
-      <c r="J32" s="8">
-        <v>4000</v>
-      </c>
-      <c r="K32" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="33" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="8">
-        <f>B34-SUM(B20:B32)</f>
-        <v>210.304</v>
-      </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8">
-        <v>0</v>
-      </c>
-      <c r="E33" s="8">
-        <v>0</v>
-      </c>
-      <c r="F33" s="8">
-        <v>0</v>
-      </c>
-      <c r="G33" s="8">
-        <v>0</v>
-      </c>
-      <c r="H33" s="8">
-        <v>0</v>
-      </c>
-      <c r="I33" s="8">
-        <v>0</v>
-      </c>
-      <c r="J33" s="8">
-        <v>0</v>
-      </c>
-      <c r="K33" s="8"/>
-    </row>
-    <row r="34" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34" s="8">
-        <v>329.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
-      <c r="J35" s="7"/>
-    </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A36" s="15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A37" s="5"/>
-    </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A38" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B38">
-        <v>0.78500000000000003</v>
-      </c>
-    </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A39" s="5"/>
-    </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A40" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="C41">
-        <v>2021</v>
-      </c>
-      <c r="D41">
-        <v>2022</v>
-      </c>
-      <c r="E41">
-        <v>2023</v>
-      </c>
-      <c r="F41">
-        <v>2024</v>
-      </c>
-      <c r="G41">
-        <v>2025</v>
-      </c>
-      <c r="H41">
-        <v>2026</v>
-      </c>
-      <c r="I41">
-        <v>2027</v>
-      </c>
-      <c r="J41">
-        <v>2028</v>
-      </c>
-      <c r="K41">
-        <v>2029</v>
-      </c>
-      <c r="L41">
-        <v>2030</v>
-      </c>
-      <c r="M41">
-        <v>2031</v>
-      </c>
-      <c r="N41">
-        <v>2032</v>
-      </c>
-      <c r="O41">
-        <v>2033</v>
-      </c>
-      <c r="P41">
-        <v>2034</v>
-      </c>
-      <c r="Q41">
-        <v>2035</v>
-      </c>
-      <c r="R41">
-        <v>2036</v>
-      </c>
-      <c r="S41">
-        <v>2037</v>
-      </c>
-      <c r="T41">
-        <v>2038</v>
-      </c>
-      <c r="U41">
-        <v>2039</v>
-      </c>
-      <c r="V41">
-        <v>2040</v>
-      </c>
-      <c r="W41">
-        <v>2041</v>
-      </c>
-      <c r="X41">
-        <v>2042</v>
-      </c>
-      <c r="Y41">
-        <v>2043</v>
-      </c>
-      <c r="Z41">
-        <v>2044</v>
-      </c>
-      <c r="AA41">
-        <v>2045</v>
-      </c>
-      <c r="AB41">
-        <v>2046</v>
-      </c>
-      <c r="AC41">
-        <v>2047</v>
-      </c>
-      <c r="AD41">
-        <v>2048</v>
-      </c>
-      <c r="AE41">
-        <v>2049</v>
-      </c>
-      <c r="AF41">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="C42" s="5">
-        <f t="shared" ref="C42:H42" si="5">SUMPRODUCT(E20:E33,$B$20:$B$33)/SUM($B$20:$B$33)*$B$38</f>
-        <v>600.15334597875574</v>
-      </c>
-      <c r="D42" s="5">
-        <f t="shared" si="5"/>
-        <v>576.45146813353574</v>
-      </c>
-      <c r="E42" s="5">
-        <f t="shared" si="5"/>
-        <v>576.45146813353574</v>
-      </c>
-      <c r="F42" s="5">
-        <f t="shared" si="5"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="G42" s="5">
-        <f t="shared" si="5"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="H42" s="5">
-        <f t="shared" si="5"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="I42" s="5">
-        <f>H42</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="J42" s="5">
-        <f t="shared" ref="J42:AF42" si="6">I42</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="K42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="L42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="M42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="N42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="O42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="P42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Q42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="R42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="S42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="T42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="U42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="V42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="W42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="X42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Y42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Z42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AA42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AB42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AC42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AD42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AE42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AF42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-    </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A43" s="5"/>
-    </row>
-    <row r="44" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A44" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="C45">
-        <v>2021</v>
-      </c>
-      <c r="D45">
-        <v>2022</v>
-      </c>
-      <c r="E45">
-        <v>2023</v>
-      </c>
-      <c r="F45">
-        <v>2024</v>
-      </c>
-      <c r="G45">
-        <v>2025</v>
-      </c>
-      <c r="H45">
-        <v>2026</v>
-      </c>
-      <c r="I45">
-        <v>2027</v>
-      </c>
-      <c r="J45">
-        <v>2028</v>
-      </c>
-      <c r="K45">
-        <v>2029</v>
-      </c>
-      <c r="L45">
-        <v>2030</v>
-      </c>
-      <c r="M45">
-        <v>2031</v>
-      </c>
-      <c r="N45">
-        <v>2032</v>
-      </c>
-      <c r="O45">
-        <v>2033</v>
-      </c>
-      <c r="P45">
-        <v>2034</v>
-      </c>
-      <c r="Q45">
-        <v>2035</v>
-      </c>
-      <c r="R45">
-        <v>2036</v>
-      </c>
-      <c r="S45">
-        <v>2037</v>
-      </c>
-      <c r="T45">
-        <v>2038</v>
-      </c>
-      <c r="U45">
-        <v>2039</v>
-      </c>
-      <c r="V45">
-        <v>2040</v>
-      </c>
-      <c r="W45">
-        <v>2041</v>
-      </c>
-      <c r="X45">
-        <v>2042</v>
-      </c>
-      <c r="Y45">
-        <v>2043</v>
-      </c>
-      <c r="Z45">
-        <v>2044</v>
-      </c>
-      <c r="AA45">
-        <v>2045</v>
-      </c>
-      <c r="AB45">
-        <v>2046</v>
-      </c>
-      <c r="AC45">
-        <v>2047</v>
-      </c>
-      <c r="AD45">
-        <v>2048</v>
-      </c>
-      <c r="AE45">
-        <v>2049</v>
-      </c>
-      <c r="AF45">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A46" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5">
-        <f t="shared" ref="C46:AF46" si="7">B4+C42</f>
-        <v>3036.0333459787557</v>
-      </c>
-      <c r="D46" s="5">
-        <f t="shared" si="7"/>
-        <v>2273.5314681335358</v>
-      </c>
-      <c r="E46" s="5">
-        <f t="shared" si="7"/>
-        <v>2371.7262681335355</v>
-      </c>
-      <c r="F46" s="5">
-        <f t="shared" si="7"/>
-        <v>2329.8343100151742</v>
-      </c>
-      <c r="G46" s="5">
-        <f t="shared" si="7"/>
-        <v>1671.1026100151744</v>
-      </c>
-      <c r="H46" s="5">
-        <f t="shared" si="7"/>
-        <v>1625.6076100151745</v>
-      </c>
-      <c r="I46" s="5">
-        <f t="shared" si="7"/>
-        <v>1591.1151100151747</v>
-      </c>
-      <c r="J46" s="5">
-        <f t="shared" si="7"/>
-        <v>1593.1401100151747</v>
-      </c>
-      <c r="K46" s="5">
-        <f t="shared" si="7"/>
-        <v>1599.8726100151744</v>
-      </c>
-      <c r="L46" s="5">
-        <f t="shared" si="7"/>
-        <v>1658.1326100151746</v>
-      </c>
-      <c r="M46" s="5">
-        <f t="shared" si="7"/>
-        <v>1713.9176100151744</v>
-      </c>
-      <c r="N46" s="5">
-        <f t="shared" si="7"/>
-        <v>1724.7001100151747</v>
-      </c>
-      <c r="O46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="P46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Q46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="R46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="S46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="T46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="U46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="V46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="W46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="X46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Y46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Z46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AA46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AB46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AC46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AD46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AE46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AF46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-    </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A47" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C47" s="5">
-        <f t="shared" ref="C47:AF47" si="8">B5+C42</f>
-        <v>7252.8733459787563</v>
-      </c>
-      <c r="D47" s="5">
-        <f t="shared" si="8"/>
-        <v>4193.501468133536</v>
-      </c>
-      <c r="E47" s="5">
-        <f t="shared" si="8"/>
-        <v>2371.7262681335355</v>
-      </c>
-      <c r="F47" s="5">
-        <f t="shared" si="8"/>
-        <v>2329.8343100151742</v>
-      </c>
-      <c r="G47" s="5">
-        <f t="shared" si="8"/>
-        <v>1671.1026100151744</v>
-      </c>
-      <c r="H47" s="5">
-        <f t="shared" si="8"/>
-        <v>1625.6076100151745</v>
-      </c>
-      <c r="I47" s="5">
-        <f t="shared" si="8"/>
-        <v>1591.1151100151747</v>
-      </c>
-      <c r="J47" s="5">
-        <f t="shared" si="8"/>
-        <v>1593.1401100151747</v>
-      </c>
-      <c r="K47" s="5">
-        <f t="shared" si="8"/>
-        <v>1599.8726100151744</v>
-      </c>
-      <c r="L47" s="5">
-        <f t="shared" si="8"/>
-        <v>1658.1326100151746</v>
-      </c>
-      <c r="M47" s="5">
-        <f t="shared" si="8"/>
-        <v>1713.9176100151744</v>
-      </c>
-      <c r="N47" s="5">
-        <f t="shared" si="8"/>
-        <v>1724.7001100151747</v>
-      </c>
-      <c r="O47" s="5">
-        <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="P47" s="5">
-        <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Q47" s="5">
-        <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="R47" s="5">
-        <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="S47" s="5">
-        <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="T47" s="5">
-        <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="U47" s="5">
-        <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="V47" s="5">
-        <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="W47" s="5">
-        <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="X47" s="5">
-        <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Y47" s="5">
-        <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Z47" s="5">
-        <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AA47" s="5">
-        <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AB47" s="5">
-        <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AC47" s="5">
-        <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AD47" s="5">
-        <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AE47" s="5">
-        <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AF47" s="5">
-        <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-    </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B59" s="17"/>
-      <c r="C59" s="18"/>
-      <c r="D59" s="18"/>
-      <c r="E59" s="18"/>
-      <c r="F59" s="18"/>
-      <c r="G59" s="18"/>
-      <c r="H59" s="18"/>
-      <c r="I59" s="18"/>
-      <c r="J59" s="18"/>
-      <c r="K59" s="18"/>
-      <c r="L59" s="16"/>
+    </row>
+    <row r="28" spans="1:31">
+      <c r="B28" s="7"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="6"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C16" r:id="rId1" xr:uid="{0B42DB82-B744-4AA0-B817-45B85EC34540}"/>
-    <hyperlink ref="C17" r:id="rId2" xr:uid="{C245D4AA-4F3C-42F0-8772-AD708218D115}"/>
-    <hyperlink ref="R21" r:id="rId3" xr:uid="{52E38CEB-73A7-4855-878F-13F2616EA324}"/>
+    <hyperlink ref="A21" r:id="rId1" tooltip="새창으로 열림" display="https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1404&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=2" xr:uid="{F3E7EE48-83EE-42B1-BAA8-2FE424469922}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC4700B1-78D7-456C-A4C4-AB085247994E}">
-  <dimension ref="A1:AL776"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBDF62BA-2B52-48EA-8513-8E5B1006C831}">
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:AF18"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="51.81640625" style="23" customWidth="1"/>
-    <col min="2" max="2" width="12.7265625" style="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.26953125" style="23" customWidth="1"/>
-    <col min="4" max="4" width="9.54296875" style="23" customWidth="1"/>
-    <col min="5" max="38" width="7.54296875" style="23" customWidth="1"/>
-    <col min="39" max="16384" width="12.54296875" style="23"/>
+    <col min="1" max="1" width="11.75" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
-      <c r="T1" s="22"/>
-      <c r="U1" s="22"/>
-      <c r="V1" s="22"/>
-      <c r="W1" s="22"/>
-      <c r="X1" s="22"/>
-      <c r="Y1" s="22"/>
-      <c r="Z1" s="22"/>
-      <c r="AA1" s="22"/>
-      <c r="AB1" s="22"/>
-      <c r="AC1" s="22"/>
-      <c r="AD1" s="22"/>
-      <c r="AE1" s="22"/>
-      <c r="AF1" s="22"/>
-      <c r="AG1" s="22"/>
-      <c r="AH1" s="22"/>
-      <c r="AI1" s="22"/>
-      <c r="AJ1" s="22"/>
-      <c r="AK1" s="22"/>
-      <c r="AL1" s="22"/>
-    </row>
-    <row r="2" spans="1:38" ht="104.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-      <c r="V2" s="25"/>
-      <c r="W2" s="25"/>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="25"/>
-      <c r="Z2" s="25"/>
-      <c r="AA2" s="25"/>
-      <c r="AB2" s="25"/>
-      <c r="AC2" s="25"/>
-      <c r="AD2" s="25"/>
-      <c r="AE2" s="25"/>
-      <c r="AF2" s="25"/>
-      <c r="AG2" s="25"/>
-      <c r="AH2" s="25"/>
-      <c r="AI2" s="25"/>
-      <c r="AJ2" s="25"/>
-      <c r="AK2" s="25"/>
-      <c r="AL2" s="25"/>
-    </row>
-    <row r="3" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="25"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="25"/>
-      <c r="W3" s="25"/>
-      <c r="X3" s="25"/>
-      <c r="Y3" s="25"/>
-      <c r="Z3" s="25"/>
-      <c r="AA3" s="25"/>
-      <c r="AB3" s="25"/>
-      <c r="AC3" s="25"/>
-      <c r="AD3" s="25"/>
-      <c r="AE3" s="25"/>
-      <c r="AF3" s="25"/>
-      <c r="AG3" s="25"/>
-      <c r="AH3" s="25"/>
-      <c r="AI3" s="25"/>
-      <c r="AJ3" s="25"/>
-      <c r="AK3" s="25"/>
-      <c r="AL3" s="25"/>
-    </row>
-    <row r="4" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="B4" s="35">
-        <v>40000</v>
-      </c>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
-      <c r="P4" s="25"/>
-      <c r="Q4" s="25"/>
-      <c r="R4" s="25"/>
-      <c r="S4" s="25"/>
-      <c r="T4" s="25"/>
-      <c r="U4" s="25"/>
-      <c r="V4" s="25"/>
-      <c r="W4" s="25"/>
-      <c r="X4" s="25"/>
-      <c r="Y4" s="25"/>
-      <c r="Z4" s="25"/>
-      <c r="AA4" s="25"/>
-      <c r="AB4" s="25"/>
-      <c r="AC4" s="25"/>
-      <c r="AD4" s="25"/>
-      <c r="AE4" s="25"/>
-      <c r="AF4" s="25"/>
-      <c r="AG4" s="25"/>
-      <c r="AH4" s="25"/>
-      <c r="AI4" s="25"/>
-      <c r="AJ4" s="25"/>
-      <c r="AK4" s="25"/>
-      <c r="AL4" s="25"/>
-    </row>
-    <row r="5" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="B5" s="35">
-        <v>7500</v>
-      </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="25"/>
-      <c r="P5" s="25"/>
-      <c r="Q5" s="25"/>
-      <c r="R5" s="25"/>
-      <c r="S5" s="25"/>
-      <c r="T5" s="25"/>
-      <c r="U5" s="25"/>
-      <c r="V5" s="25"/>
-      <c r="W5" s="25"/>
-      <c r="X5" s="25"/>
-      <c r="Y5" s="25"/>
-      <c r="Z5" s="25"/>
-      <c r="AA5" s="25"/>
-      <c r="AB5" s="25"/>
-      <c r="AC5" s="25"/>
-      <c r="AD5" s="25"/>
-      <c r="AE5" s="25"/>
-      <c r="AF5" s="25"/>
-      <c r="AG5" s="25"/>
-      <c r="AH5" s="25"/>
-      <c r="AI5" s="25"/>
-      <c r="AJ5" s="25"/>
-      <c r="AK5" s="25"/>
-      <c r="AL5" s="25"/>
-    </row>
-    <row r="6" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="25"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="25"/>
-      <c r="P6" s="25"/>
-      <c r="Q6" s="25"/>
-      <c r="R6" s="25"/>
-      <c r="S6" s="25"/>
-      <c r="T6" s="25"/>
-      <c r="U6" s="25"/>
-      <c r="V6" s="25"/>
-      <c r="W6" s="25"/>
-      <c r="X6" s="25"/>
-      <c r="Y6" s="25"/>
-      <c r="Z6" s="25"/>
-      <c r="AA6" s="25"/>
-      <c r="AB6" s="25"/>
-      <c r="AC6" s="25"/>
-      <c r="AD6" s="25"/>
-      <c r="AE6" s="25"/>
-      <c r="AF6" s="25"/>
-      <c r="AG6" s="25"/>
-      <c r="AH6" s="25"/>
-      <c r="AI6" s="25"/>
-      <c r="AJ6" s="25"/>
-      <c r="AK6" s="25"/>
-      <c r="AL6" s="25"/>
-    </row>
-    <row r="7" spans="1:38" ht="13" x14ac:dyDescent="0.3">
-      <c r="A7" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" s="27">
-        <f>B4*$B$16*$B$14</f>
-        <v>27004</v>
-      </c>
-    </row>
-    <row r="8" spans="1:38" ht="13" x14ac:dyDescent="0.3">
-      <c r="A8" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8" s="27">
-        <f>B4*B14</f>
-        <v>31400</v>
-      </c>
-    </row>
-    <row r="9" spans="1:38" ht="13" x14ac:dyDescent="0.3">
-      <c r="A9" s="26"/>
-      <c r="B9" s="27"/>
-    </row>
-    <row r="10" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="23">
+    <row r="1" spans="1:32">
+      <c r="A1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32">
+      <c r="A2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32">
+      <c r="C3">
+        <v>2021</v>
+      </c>
+      <c r="D3">
+        <v>2022</v>
+      </c>
+      <c r="E3">
         <v>2023</v>
       </c>
-      <c r="C10" s="23">
+      <c r="F3">
         <v>2024</v>
       </c>
-      <c r="D10" s="23">
+      <c r="G3">
         <v>2025</v>
       </c>
-      <c r="E10" s="23">
+    </row>
+    <row r="4" spans="1:32">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4">
+        <v>33560</v>
+      </c>
+      <c r="D4">
+        <v>29386</v>
+      </c>
+      <c r="E4">
+        <v>11900</v>
+      </c>
+      <c r="F4">
+        <v>17000</v>
+      </c>
+      <c r="G4">
+        <v>19812</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32">
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5">
+        <v>15000</v>
+      </c>
+      <c r="D5">
+        <v>30000</v>
+      </c>
+      <c r="E5">
+        <v>35000</v>
+      </c>
+      <c r="F5">
+        <v>35000</v>
+      </c>
+      <c r="G5">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6">
+        <v>1650</v>
+      </c>
+      <c r="D6">
+        <v>1500</v>
+      </c>
+      <c r="E6">
+        <v>1260</v>
+      </c>
+      <c r="F6">
+        <v>1153</v>
+      </c>
+      <c r="G6">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7">
+        <v>3150</v>
+      </c>
+      <c r="D7">
+        <v>2628</v>
+      </c>
+      <c r="E7">
+        <v>1946</v>
+      </c>
+      <c r="F7">
+        <v>2022</v>
+      </c>
+      <c r="G7">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32">
+      <c r="A10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10">
+        <v>1363.18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32">
+      <c r="A11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11">
+        <v>0.73191600598044548</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32">
+      <c r="A13" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32">
+      <c r="A14" s="5"/>
+      <c r="C14">
+        <v>2021</v>
+      </c>
+      <c r="D14">
+        <v>2022</v>
+      </c>
+      <c r="E14">
+        <v>2023</v>
+      </c>
+      <c r="F14">
+        <v>2024</v>
+      </c>
+      <c r="G14">
+        <v>2025</v>
+      </c>
+      <c r="H14">
         <v>2026</v>
       </c>
-      <c r="F10" s="23">
+      <c r="I14">
         <v>2027</v>
       </c>
-      <c r="G10" s="23">
+      <c r="J14">
         <v>2028</v>
       </c>
-      <c r="H10" s="23">
+      <c r="K14">
         <v>2029</v>
       </c>
-      <c r="I10" s="23">
+      <c r="L14">
         <v>2030</v>
       </c>
-      <c r="J10" s="23">
+      <c r="M14">
         <v>2031</v>
       </c>
-      <c r="K10" s="23">
+      <c r="N14">
         <v>2032</v>
       </c>
-    </row>
-    <row r="11" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="B11" s="36">
-        <f>C36</f>
-        <v>10121.162702145082</v>
-      </c>
-      <c r="C11" s="36">
-        <f t="shared" ref="C11:K11" si="0">D36</f>
-        <v>10059.772494365814</v>
-      </c>
-      <c r="D11" s="36">
+      <c r="O14">
+        <v>2033</v>
+      </c>
+      <c r="P14">
+        <v>2034</v>
+      </c>
+      <c r="Q14">
+        <v>2035</v>
+      </c>
+      <c r="R14">
+        <v>2036</v>
+      </c>
+      <c r="S14">
+        <v>2037</v>
+      </c>
+      <c r="T14">
+        <v>2038</v>
+      </c>
+      <c r="U14">
+        <v>2039</v>
+      </c>
+      <c r="V14">
+        <v>2040</v>
+      </c>
+      <c r="W14">
+        <v>2041</v>
+      </c>
+      <c r="X14">
+        <v>2042</v>
+      </c>
+      <c r="Y14">
+        <v>2043</v>
+      </c>
+      <c r="Z14">
+        <v>2044</v>
+      </c>
+      <c r="AA14">
+        <v>2045</v>
+      </c>
+      <c r="AB14">
+        <v>2046</v>
+      </c>
+      <c r="AC14">
+        <v>2047</v>
+      </c>
+      <c r="AD14">
+        <v>2048</v>
+      </c>
+      <c r="AE14">
+        <v>2049</v>
+      </c>
+      <c r="AF14">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="17">
+        <f>10000*C4/$B$10*$B$11</f>
+        <v>180189.71200211087</v>
+      </c>
+      <c r="D15" s="17">
+        <f t="shared" ref="D15:F15" si="0">10000*D4/$B$10*$B$11</f>
+        <v>157778.75080137159</v>
+      </c>
+      <c r="E15" s="17">
         <f t="shared" si="0"/>
-        <v>10050.763799597085</v>
-      </c>
-      <c r="E11" s="36">
+        <v>63893.253063918928</v>
+      </c>
+      <c r="F15" s="17">
         <f t="shared" si="0"/>
-        <v>10127.428607069427</v>
-      </c>
-      <c r="F11" s="36">
-        <f t="shared" si="0"/>
-        <v>10269.11524721545</v>
-      </c>
-      <c r="G11" s="36">
-        <f t="shared" si="0"/>
-        <v>10350.781370900584</v>
-      </c>
-      <c r="H11" s="36">
-        <f t="shared" si="0"/>
-        <v>10353.674088089921</v>
-      </c>
-      <c r="I11" s="36">
-        <f t="shared" si="0"/>
-        <v>10294.239800360298</v>
-      </c>
-      <c r="J11" s="36">
-        <f t="shared" si="0"/>
-        <v>10251.903689786537</v>
-      </c>
-      <c r="K11" s="36">
-        <f t="shared" si="0"/>
-        <v>10279.777009851599</v>
-      </c>
-    </row>
-    <row r="13" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="22"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="22"/>
-      <c r="R13" s="22"/>
-      <c r="S13" s="22"/>
-      <c r="T13" s="22"/>
-      <c r="U13" s="22"/>
-      <c r="V13" s="22"/>
-      <c r="W13" s="22"/>
-      <c r="X13" s="22"/>
-      <c r="Y13" s="22"/>
-      <c r="Z13" s="22"/>
-      <c r="AA13" s="22"/>
-      <c r="AB13" s="22"/>
-      <c r="AC13" s="22"/>
-      <c r="AD13" s="22"/>
-      <c r="AE13" s="22"/>
-      <c r="AF13" s="22"/>
-      <c r="AG13" s="22"/>
-      <c r="AH13" s="22"/>
-      <c r="AI13" s="22"/>
-      <c r="AJ13" s="22"/>
-      <c r="AK13" s="22"/>
-      <c r="AL13" s="22"/>
-    </row>
-    <row r="14" spans="1:38" ht="13" x14ac:dyDescent="0.3">
-      <c r="A14" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="B14" s="26">
-        <v>0.78500000000000003</v>
-      </c>
-    </row>
-    <row r="15" spans="1:38" ht="13" x14ac:dyDescent="0.3">
-      <c r="A15" s="26"/>
-    </row>
-    <row r="16" spans="1:38" ht="13" x14ac:dyDescent="0.3">
-      <c r="A16" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="B16" s="26">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="17" spans="1:33" ht="13" x14ac:dyDescent="0.3">
-      <c r="A17" s="26"/>
-    </row>
-    <row r="18" spans="1:33" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="1:33" ht="13" x14ac:dyDescent="0.3">
-      <c r="A19" s="26" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:33" ht="13" x14ac:dyDescent="0.3">
-      <c r="A20" s="26" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="21" spans="1:33" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="1:33" ht="39" x14ac:dyDescent="0.3">
-      <c r="A22" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="23" spans="1:33" ht="26" x14ac:dyDescent="0.3">
-      <c r="A23" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="D23" s="27">
-        <f>B5*B14</f>
-        <v>5887.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:33" ht="26" x14ac:dyDescent="0.3">
-      <c r="A24" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="B24" s="24">
-        <v>3</v>
-      </c>
-      <c r="C24" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="D24" s="27">
-        <f>D23</f>
-        <v>5887.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:33" ht="26" x14ac:dyDescent="0.3">
-      <c r="A25" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="B25" s="29">
-        <v>44657</v>
-      </c>
-      <c r="C25" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" s="27">
-        <f>B4*B14</f>
-        <v>31400</v>
-      </c>
-    </row>
-    <row r="26" spans="1:33" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="1:33" ht="13" x14ac:dyDescent="0.3">
-      <c r="A27" s="26" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="28" spans="1:33" ht="13" x14ac:dyDescent="0.3">
-      <c r="A28" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="30"/>
-      <c r="K28" s="30"/>
-      <c r="L28" s="30"/>
-      <c r="M28" s="30"/>
-      <c r="N28" s="30"/>
-      <c r="O28" s="30"/>
-      <c r="P28" s="30"/>
-      <c r="Q28" s="30"/>
-      <c r="R28" s="30"/>
-      <c r="S28" s="30"/>
-      <c r="T28" s="30"/>
-      <c r="U28" s="30"/>
-      <c r="V28" s="30"/>
-      <c r="W28" s="30"/>
-      <c r="X28" s="30"/>
-      <c r="Y28" s="30"/>
-      <c r="Z28" s="30"/>
-      <c r="AA28" s="30"/>
-      <c r="AB28" s="30"/>
-      <c r="AC28" s="30"/>
-      <c r="AD28" s="30"/>
-      <c r="AE28" s="30"/>
-      <c r="AF28" s="30"/>
-      <c r="AG28" s="30"/>
-    </row>
-    <row r="29" spans="1:33" ht="13" x14ac:dyDescent="0.3">
-      <c r="A29" s="31"/>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="30"/>
-      <c r="P29" s="30"/>
-      <c r="Q29" s="30"/>
-      <c r="R29" s="30"/>
-      <c r="S29" s="30"/>
-      <c r="T29" s="30"/>
-      <c r="U29" s="30"/>
-      <c r="V29" s="30"/>
-      <c r="W29" s="30"/>
-      <c r="X29" s="30"/>
-      <c r="Y29" s="30"/>
-      <c r="Z29" s="30"/>
-      <c r="AA29" s="30"/>
-      <c r="AB29" s="30"/>
-      <c r="AC29" s="30"/>
-      <c r="AD29" s="30"/>
-      <c r="AE29" s="30"/>
-      <c r="AF29" s="30"/>
-      <c r="AG29" s="30"/>
-    </row>
-    <row r="30" spans="1:33" ht="13" x14ac:dyDescent="0.3">
-      <c r="A30" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
-      <c r="H30" s="30"/>
-      <c r="I30" s="30"/>
-      <c r="J30" s="30"/>
-      <c r="K30" s="30"/>
-      <c r="L30" s="30"/>
-      <c r="M30" s="30"/>
-      <c r="N30" s="30"/>
-      <c r="O30" s="30"/>
-      <c r="P30" s="30"/>
-      <c r="Q30" s="30"/>
-      <c r="R30" s="30"/>
-      <c r="S30" s="30"/>
-      <c r="T30" s="30"/>
-      <c r="U30" s="30"/>
-      <c r="V30" s="30"/>
-      <c r="W30" s="30"/>
-      <c r="X30" s="30"/>
-      <c r="Y30" s="30"/>
-      <c r="Z30" s="30"/>
-      <c r="AA30" s="30"/>
-      <c r="AB30" s="30"/>
-      <c r="AC30" s="30"/>
-      <c r="AD30" s="30"/>
-      <c r="AE30" s="30"/>
-      <c r="AF30" s="30"/>
-      <c r="AG30" s="30"/>
-    </row>
-    <row r="31" spans="1:33" ht="13" x14ac:dyDescent="0.3">
-      <c r="A31" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="B31" s="32">
-        <v>2022</v>
-      </c>
-      <c r="C31" s="32">
-        <v>2023</v>
-      </c>
-      <c r="D31" s="32">
-        <v>2024</v>
-      </c>
-      <c r="E31" s="32">
-        <v>2025</v>
-      </c>
-      <c r="F31" s="32">
-        <v>2026</v>
-      </c>
-      <c r="G31" s="32">
-        <v>2027</v>
-      </c>
-      <c r="H31" s="32">
-        <v>2028</v>
-      </c>
-      <c r="I31" s="32">
-        <v>2029</v>
-      </c>
-      <c r="J31" s="32">
-        <v>2030</v>
-      </c>
-      <c r="K31" s="32">
-        <v>2031</v>
-      </c>
-      <c r="L31" s="32">
-        <v>2032</v>
-      </c>
-      <c r="M31" s="32">
-        <v>2033</v>
-      </c>
-      <c r="N31" s="32">
-        <v>2034</v>
-      </c>
-      <c r="O31" s="32">
-        <v>2035</v>
-      </c>
-      <c r="P31" s="32">
-        <v>2036</v>
-      </c>
-      <c r="Q31" s="32">
-        <v>2037</v>
-      </c>
-      <c r="R31" s="32">
-        <v>2038</v>
-      </c>
-      <c r="S31" s="32">
-        <v>2039</v>
-      </c>
-      <c r="T31" s="32">
-        <v>2040</v>
-      </c>
-      <c r="U31" s="32">
-        <v>2041</v>
-      </c>
-      <c r="V31" s="32">
-        <v>2042</v>
-      </c>
-      <c r="W31" s="32">
-        <v>2043</v>
-      </c>
-      <c r="X31" s="32">
-        <v>2044</v>
-      </c>
-      <c r="Y31" s="32">
-        <v>2045</v>
-      </c>
-      <c r="Z31" s="32">
-        <v>2046</v>
-      </c>
-      <c r="AA31" s="32">
-        <v>2047</v>
-      </c>
-      <c r="AB31" s="32">
-        <v>2048</v>
-      </c>
-      <c r="AC31" s="32">
-        <v>2049</v>
-      </c>
-      <c r="AD31" s="32">
-        <v>2050</v>
-      </c>
-      <c r="AE31" s="30"/>
-      <c r="AF31" s="30"/>
-    </row>
-    <row r="32" spans="1:33" ht="13" x14ac:dyDescent="0.3">
-      <c r="A32" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="B32" s="33">
-        <v>652.15881300000001</v>
-      </c>
-      <c r="C32" s="33">
-        <v>675.13665800000001</v>
-      </c>
-      <c r="D32" s="33">
-        <v>689.60467500000004</v>
-      </c>
-      <c r="E32" s="33">
-        <v>691.51690699999995</v>
-      </c>
-      <c r="F32" s="33">
-        <v>688.42425500000002</v>
-      </c>
-      <c r="G32" s="33">
-        <v>684.18414299999995</v>
-      </c>
-      <c r="H32" s="33">
-        <v>682.62188700000002</v>
-      </c>
-      <c r="I32" s="33">
-        <v>679.86218299999996</v>
-      </c>
-      <c r="J32" s="33">
-        <v>678.07775900000001</v>
-      </c>
-      <c r="K32" s="33">
-        <v>677.36639400000001</v>
-      </c>
-      <c r="L32" s="33">
-        <v>675.92620799999997</v>
-      </c>
-      <c r="M32" s="33">
-        <v>676.86370799999997</v>
-      </c>
-      <c r="N32" s="33">
-        <v>681.45581100000004</v>
-      </c>
-      <c r="O32" s="33">
-        <v>687.30078100000003</v>
-      </c>
-      <c r="P32" s="33">
-        <v>692.37145999999996</v>
-      </c>
-      <c r="Q32" s="33">
-        <v>698.31860400000005</v>
-      </c>
-      <c r="R32" s="33">
-        <v>703.59320100000002</v>
-      </c>
-      <c r="S32" s="33">
-        <v>709.57092299999999</v>
-      </c>
-      <c r="T32" s="33">
-        <v>711.90655500000003</v>
-      </c>
-      <c r="U32" s="33">
-        <v>714.37567100000001</v>
-      </c>
-      <c r="V32" s="33">
-        <v>716.10638400000005</v>
-      </c>
-      <c r="W32" s="33">
-        <v>717.97564699999998</v>
-      </c>
-      <c r="X32" s="33">
-        <v>723.98962400000005</v>
-      </c>
-      <c r="Y32" s="33">
-        <v>729.19946300000004</v>
-      </c>
-      <c r="Z32" s="33">
-        <v>732.66320800000005</v>
-      </c>
-      <c r="AA32" s="33">
-        <v>734.38165300000003</v>
-      </c>
-      <c r="AB32" s="33">
-        <v>739.21014400000001</v>
-      </c>
-      <c r="AC32" s="33">
-        <v>745.07336399999997</v>
-      </c>
-      <c r="AD32" s="33">
-        <v>1035.5</v>
-      </c>
-      <c r="AE32" s="34"/>
-      <c r="AF32" s="30"/>
-    </row>
-    <row r="33" spans="1:32" ht="13" x14ac:dyDescent="0.3">
-      <c r="A33" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="B33" s="33">
-        <v>252.12297100000001</v>
-      </c>
-      <c r="C33" s="33">
-        <v>262.199432</v>
-      </c>
-      <c r="D33" s="33">
-        <v>276.18127399999997</v>
-      </c>
-      <c r="E33" s="33">
-        <v>286.01892099999998</v>
-      </c>
-      <c r="F33" s="33">
-        <v>290.46655299999998</v>
-      </c>
-      <c r="G33" s="33">
-        <v>292.43240400000002</v>
-      </c>
-      <c r="H33" s="33">
-        <v>293.63424700000002</v>
-      </c>
-      <c r="I33" s="33">
-        <v>296.173248</v>
-      </c>
-      <c r="J33" s="33">
-        <v>298.12170400000002</v>
-      </c>
-      <c r="K33" s="33">
-        <v>300.39685100000003</v>
-      </c>
-      <c r="L33" s="33">
-        <v>303.257294</v>
-      </c>
-      <c r="M33" s="33">
-        <v>305.71603399999998</v>
-      </c>
-      <c r="N33" s="33">
-        <v>309.26257299999997</v>
-      </c>
-      <c r="O33" s="33">
-        <v>314.79812600000002</v>
-      </c>
-      <c r="P33" s="33">
-        <v>321.14746100000002</v>
-      </c>
-      <c r="Q33" s="33">
-        <v>327.09249899999998</v>
-      </c>
-      <c r="R33" s="33">
-        <v>333.56478900000002</v>
-      </c>
-      <c r="S33" s="33">
-        <v>339.75351000000001</v>
-      </c>
-      <c r="T33" s="33">
-        <v>346.38189699999998</v>
-      </c>
-      <c r="U33" s="33">
-        <v>351.209137</v>
-      </c>
-      <c r="V33" s="33">
-        <v>355.95761099999999</v>
-      </c>
-      <c r="W33" s="33">
-        <v>360.42837500000002</v>
-      </c>
-      <c r="X33" s="33">
-        <v>364.902466</v>
-      </c>
-      <c r="Y33" s="33">
-        <v>371.72610500000002</v>
-      </c>
-      <c r="Z33" s="33">
-        <v>378.28823899999998</v>
-      </c>
-      <c r="AA33" s="33">
-        <v>383.89129600000001</v>
-      </c>
-      <c r="AB33" s="33">
-        <v>388.47567700000002</v>
-      </c>
-      <c r="AC33" s="33">
-        <v>394.81222500000001</v>
-      </c>
-      <c r="AD33" s="33">
-        <v>401.96115099999997</v>
-      </c>
-      <c r="AE33" s="34"/>
-      <c r="AF33" s="30"/>
-    </row>
-    <row r="34" spans="1:32" ht="13" x14ac:dyDescent="0.3">
-      <c r="A34" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="B34" s="33">
-        <v>180.61982699999999</v>
-      </c>
-      <c r="C34" s="33">
-        <v>186.49350000000001</v>
-      </c>
-      <c r="D34" s="33">
-        <v>188.82283000000001</v>
-      </c>
-      <c r="E34" s="33">
-        <v>190.626938</v>
-      </c>
-      <c r="F34" s="33">
-        <v>195.106979</v>
-      </c>
-      <c r="G34" s="33">
-        <v>202.50727800000001</v>
-      </c>
-      <c r="H34" s="33">
-        <v>207.005585</v>
-      </c>
-      <c r="I34" s="33">
-        <v>207.12138400000001</v>
-      </c>
-      <c r="J34" s="33">
-        <v>203.823837</v>
-      </c>
-      <c r="K34" s="33">
-        <v>201.78428600000001</v>
-      </c>
-      <c r="L34" s="33">
-        <v>203.63635300000001</v>
-      </c>
-      <c r="M34" s="33">
-        <v>206.92961099999999</v>
-      </c>
-      <c r="N34" s="33">
-        <v>209.69859299999999</v>
-      </c>
-      <c r="O34" s="33">
-        <v>212.967072</v>
-      </c>
-      <c r="P34" s="33">
-        <v>216.125214</v>
-      </c>
-      <c r="Q34" s="33">
-        <v>219.188492</v>
-      </c>
-      <c r="R34" s="33">
-        <v>221.84333799999999</v>
-      </c>
-      <c r="S34" s="33">
-        <v>224.323059</v>
-      </c>
-      <c r="T34" s="33">
-        <v>227.32418799999999</v>
-      </c>
-      <c r="U34" s="33">
-        <v>230.371872</v>
-      </c>
-      <c r="V34" s="33">
-        <v>232.498154</v>
-      </c>
-      <c r="W34" s="33">
-        <v>235.21517900000001</v>
-      </c>
-      <c r="X34" s="33">
-        <v>236.05999800000001</v>
-      </c>
-      <c r="Y34" s="33">
-        <v>234.92872600000001</v>
-      </c>
-      <c r="Z34" s="33">
-        <v>234.37702899999999</v>
-      </c>
-      <c r="AA34" s="33">
-        <v>235.44674699999999</v>
-      </c>
-      <c r="AB34" s="33">
-        <v>237.52796900000001</v>
-      </c>
-      <c r="AC34" s="33">
-        <v>239.052933</v>
-      </c>
-      <c r="AD34" s="33">
-        <v>241.633881</v>
-      </c>
-      <c r="AE34" s="34"/>
-      <c r="AF34" s="30"/>
-    </row>
-    <row r="36" spans="1:32" ht="13" x14ac:dyDescent="0.3">
-      <c r="A36" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="B36" s="27">
-        <f t="shared" ref="B36:AD36" si="1">SUMPRODUCT(B32:B34,$D$23:$D$25)/SUM(B32:B34)</f>
-        <v>10134.948146095066</v>
-      </c>
-      <c r="C36" s="27">
+        <v>91276.075805598477</v>
+      </c>
+      <c r="G15" s="17">
+        <f>10000*G4/$B$10*$B$11</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="H15" s="17">
+        <f>$G15</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="I15" s="17">
+        <f t="shared" ref="I15:AF18" si="1">$G15</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="J15" s="17">
         <f t="shared" si="1"/>
-        <v>10121.162702145082</v>
-      </c>
-      <c r="D36" s="27">
+        <v>106374.21258003041</v>
+      </c>
+      <c r="K15" s="17">
         <f t="shared" si="1"/>
-        <v>10059.772494365814</v>
-      </c>
-      <c r="E36" s="27">
+        <v>106374.21258003041</v>
+      </c>
+      <c r="L15" s="17">
         <f t="shared" si="1"/>
-        <v>10050.763799597085</v>
-      </c>
-      <c r="F36" s="27">
+        <v>106374.21258003041</v>
+      </c>
+      <c r="M15" s="17">
         <f t="shared" si="1"/>
-        <v>10127.428607069427</v>
-      </c>
-      <c r="G36" s="27">
+        <v>106374.21258003041</v>
+      </c>
+      <c r="N15" s="17">
         <f t="shared" si="1"/>
-        <v>10269.11524721545</v>
-      </c>
-      <c r="H36" s="27">
+        <v>106374.21258003041</v>
+      </c>
+      <c r="O15" s="17">
         <f t="shared" si="1"/>
-        <v>10350.781370900584</v>
-      </c>
-      <c r="I36" s="27">
+        <v>106374.21258003041</v>
+      </c>
+      <c r="P15" s="17">
         <f t="shared" si="1"/>
-        <v>10353.674088089921</v>
-      </c>
-      <c r="J36" s="27">
+        <v>106374.21258003041</v>
+      </c>
+      <c r="Q15" s="17">
         <f t="shared" si="1"/>
-        <v>10294.239800360298</v>
-      </c>
-      <c r="K36" s="27">
+        <v>106374.21258003041</v>
+      </c>
+      <c r="R15" s="17">
         <f t="shared" si="1"/>
-        <v>10251.903689786537</v>
-      </c>
-      <c r="L36" s="27">
+        <v>106374.21258003041</v>
+      </c>
+      <c r="S15" s="17">
         <f t="shared" si="1"/>
-        <v>10279.777009851599</v>
-      </c>
-      <c r="M36" s="27">
+        <v>106374.21258003041</v>
+      </c>
+      <c r="T15" s="17">
         <f t="shared" si="1"/>
-        <v>10325.709491436844</v>
-      </c>
-      <c r="N36" s="27">
+        <v>106374.21258003041</v>
+      </c>
+      <c r="U15" s="17">
         <f t="shared" si="1"/>
-        <v>10344.230833049938</v>
-      </c>
-      <c r="O36" s="27">
+        <v>106374.21258003041</v>
+      </c>
+      <c r="V15" s="17">
         <f t="shared" si="1"/>
-        <v>10359.12748221428</v>
-      </c>
-      <c r="P36" s="27">
+        <v>106374.21258003041</v>
+      </c>
+      <c r="W15" s="17">
         <f t="shared" si="1"/>
-        <v>10371.638430973771</v>
-      </c>
-      <c r="Q36" s="27">
+        <v>106374.21258003041</v>
+      </c>
+      <c r="X15" s="17">
         <f t="shared" si="1"/>
-        <v>10380.548547191598</v>
-      </c>
-      <c r="R36" s="27">
+        <v>106374.21258003041</v>
+      </c>
+      <c r="Y15" s="17">
         <f t="shared" si="1"/>
-        <v>10382.950508948947</v>
-      </c>
-      <c r="S36" s="27">
+        <v>106374.21258003041</v>
+      </c>
+      <c r="Z15" s="17">
         <f t="shared" si="1"/>
-        <v>10380.927010758403</v>
-      </c>
-      <c r="T36" s="27">
+        <v>106374.21258003041</v>
+      </c>
+      <c r="AA15" s="17">
         <f t="shared" si="1"/>
-        <v>10398.663134138134</v>
-      </c>
-      <c r="U36" s="27">
+        <v>106374.21258003041</v>
+      </c>
+      <c r="AB15" s="17">
         <f t="shared" si="1"/>
-        <v>10422.653431517481</v>
-      </c>
-      <c r="V36" s="27">
+        <v>106374.21258003041</v>
+      </c>
+      <c r="AC15" s="17">
         <f t="shared" si="1"/>
-        <v>10434.319910781423</v>
-      </c>
-      <c r="W36" s="27">
+        <v>106374.21258003041</v>
+      </c>
+      <c r="AD15" s="17">
         <f t="shared" si="1"/>
-        <v>10455.739600691937</v>
-      </c>
-      <c r="X36" s="27">
+        <v>106374.21258003041</v>
+      </c>
+      <c r="AE15" s="17">
         <f t="shared" si="1"/>
-        <v>10432.932814907192</v>
-      </c>
-      <c r="Y36" s="27">
+        <v>106374.21258003041</v>
+      </c>
+      <c r="AF15" s="17">
         <f t="shared" si="1"/>
-        <v>10374.231186923143</v>
-      </c>
-      <c r="Z36" s="27">
+        <v>106374.21258003041</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32">
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="17">
+        <f t="shared" ref="C16:G18" si="2">10000*C5/$B$10*$B$11</f>
+        <v>80537.713946116302</v>
+      </c>
+      <c r="D16" s="17">
+        <f t="shared" si="2"/>
+        <v>161075.4278922326</v>
+      </c>
+      <c r="E16" s="17">
+        <f t="shared" si="2"/>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="F16" s="17">
+        <f t="shared" si="2"/>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="G16" s="17">
+        <f t="shared" si="2"/>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="H16" s="17">
+        <f t="shared" ref="H16:W18" si="3">$G16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="I16" s="17">
+        <f t="shared" si="3"/>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="J16" s="17">
+        <f t="shared" si="3"/>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="K16" s="17">
+        <f t="shared" si="3"/>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="L16" s="17">
+        <f t="shared" si="3"/>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="M16" s="17">
+        <f t="shared" si="3"/>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="N16" s="17">
+        <f t="shared" si="3"/>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="O16" s="17">
+        <f t="shared" si="3"/>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="P16" s="17">
+        <f t="shared" si="3"/>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="Q16" s="17">
+        <f t="shared" si="3"/>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="R16" s="17">
+        <f t="shared" si="3"/>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="S16" s="17">
+        <f t="shared" si="3"/>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="T16" s="17">
+        <f t="shared" si="3"/>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="U16" s="17">
+        <f t="shared" si="3"/>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="V16" s="17">
+        <f t="shared" si="3"/>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="W16" s="17">
+        <f t="shared" si="3"/>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="X16" s="17">
         <f t="shared" si="1"/>
-        <v>10332.172107247137</v>
-      </c>
-      <c r="AA36" s="27">
+        <v>187921.33254093802</v>
+      </c>
+      <c r="Y16" s="17">
         <f t="shared" si="1"/>
-        <v>10324.781329795693</v>
-      </c>
-      <c r="AB36" s="27">
+        <v>187921.33254093802</v>
+      </c>
+      <c r="Z16" s="17">
         <f t="shared" si="1"/>
-        <v>10326.315629830769</v>
-      </c>
-      <c r="AC36" s="27">
+        <v>187921.33254093802</v>
+      </c>
+      <c r="AA16" s="17">
         <f t="shared" si="1"/>
-        <v>10310.34979051626</v>
-      </c>
-      <c r="AD36" s="27">
+        <v>187921.33254093802</v>
+      </c>
+      <c r="AB16" s="17">
         <f t="shared" si="1"/>
-        <v>9558.932689351499</v>
-      </c>
-    </row>
-    <row r="37" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="38" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="40" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="41" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="42" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="43" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="44" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="45" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="46" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="47" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="48" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="49" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="50" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="51" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="52" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="53" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="54" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="55" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="56" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="57" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="58" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="59" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="60" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="61" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="62" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="63" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="64" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="65" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="66" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="67" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="68" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="69" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="70" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="71" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="72" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="73" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="74" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="75" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="76" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="77" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="78" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="79" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="80" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="81" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="82" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="83" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="84" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="85" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="86" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="87" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="88" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="89" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="90" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="91" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="92" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="93" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="94" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="95" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="96" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="97" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="98" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="99" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="100" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="101" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="102" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="103" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="104" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="105" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="106" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="107" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="108" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="109" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="110" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="111" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="112" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="113" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="114" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="115" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="116" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="117" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="118" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="119" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="120" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="121" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="122" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="123" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="124" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="125" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="126" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="127" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="128" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="129" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="130" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="131" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="132" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="133" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="134" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="135" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="136" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="137" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="138" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="139" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="140" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="141" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="142" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="143" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="144" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="145" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="146" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="147" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="148" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="149" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="150" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="151" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="152" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="153" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="154" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="155" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="156" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="157" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="158" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="159" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="160" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="161" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="162" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="163" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="164" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="165" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="166" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="167" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="168" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="169" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="170" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="171" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="172" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="173" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="174" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="175" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="176" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="177" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="178" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="179" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="180" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="181" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="182" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="183" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="184" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="185" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="186" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="187" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="188" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="189" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="190" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="191" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="192" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="193" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="194" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="195" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="196" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="197" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="198" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="199" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="200" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="201" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="202" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="203" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="204" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="205" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="206" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="207" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="208" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="209" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="210" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="211" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="212" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="213" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="214" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="215" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="216" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="217" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="218" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="219" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="220" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="221" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="222" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="223" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="224" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="225" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="226" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="227" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="228" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="229" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="230" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="231" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="232" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="233" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="234" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="235" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="236" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="237" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="238" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="239" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="240" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="241" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="242" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="243" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="244" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="245" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="246" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="247" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="248" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="249" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="250" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="251" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="252" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="253" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="254" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="255" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="256" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="257" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="258" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="259" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="260" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="261" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="262" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="263" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="264" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="265" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="266" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="267" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="268" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="269" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="270" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="271" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="272" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="273" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="274" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="275" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="276" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="277" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="278" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="279" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="280" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="281" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="282" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="283" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="284" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="285" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="286" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="287" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="288" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="289" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="290" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="291" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="292" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="293" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="294" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="295" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="296" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="297" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="298" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="299" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="300" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="301" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="302" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="303" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="304" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="305" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="306" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="307" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="308" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="309" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="310" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="311" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="312" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="313" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="314" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="315" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="316" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="317" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="318" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="319" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="320" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="321" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="322" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="323" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="324" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="325" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="326" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="327" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="328" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="329" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="330" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="331" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="332" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="333" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="334" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="335" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="336" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="337" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="338" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="339" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="340" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="341" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="342" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="343" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="344" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="345" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="346" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="347" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="348" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="349" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="350" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="351" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="352" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="353" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="354" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="355" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="356" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="357" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="358" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="359" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="360" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="361" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="362" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="363" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="364" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="365" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="366" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="367" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="368" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="369" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="370" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="371" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="372" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="373" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="374" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="375" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="376" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="377" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="378" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="379" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="380" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="381" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="382" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="383" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="384" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="385" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="386" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="387" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="388" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="389" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="390" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="391" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="392" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="393" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="394" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="395" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="396" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="397" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="398" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="399" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="400" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="401" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="402" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="403" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="404" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="405" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="406" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="407" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="408" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="409" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="410" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="411" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="412" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="413" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="414" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="415" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="416" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="417" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="418" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="419" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="420" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="421" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="422" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="423" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="424" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="425" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="426" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="427" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="428" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="429" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="430" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="431" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="432" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="433" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="434" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="435" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="436" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="437" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="438" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="439" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="440" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="441" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="442" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="443" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="444" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="445" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="446" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="447" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="448" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="449" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="450" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="451" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="452" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="453" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="454" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="455" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="456" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="457" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="458" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="459" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="460" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="461" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="462" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="463" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="464" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="465" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="466" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="467" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="468" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="469" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="470" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="471" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="472" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="473" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="474" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="475" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="476" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="477" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="478" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="479" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="480" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="481" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="482" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="483" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="484" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="485" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="486" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="487" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="488" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="489" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="490" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="491" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="492" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="493" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="494" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="495" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="496" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="497" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="498" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="499" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="500" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="501" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="502" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="503" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="504" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="505" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="506" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="507" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="508" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="509" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="510" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="511" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="512" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="513" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="514" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="515" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="516" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="517" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="518" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="519" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="520" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="521" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="522" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="523" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="524" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="525" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="526" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="527" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="528" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="529" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="530" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="531" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="532" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="533" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="534" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="535" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="536" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="537" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="538" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="539" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="540" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="541" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="542" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="543" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="544" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="545" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="546" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="547" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="548" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="549" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="550" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="551" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="552" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="553" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="554" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="555" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="556" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="557" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="558" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="559" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="560" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="561" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="562" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="563" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="564" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="565" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="566" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="567" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="568" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="569" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="570" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="571" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="572" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="573" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="574" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="575" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="576" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="577" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="578" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="579" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="580" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="581" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="582" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="583" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="584" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="585" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="586" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="587" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="588" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="589" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="590" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="591" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="592" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="593" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="594" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="595" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="596" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="597" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="598" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="599" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="600" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="601" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="602" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="603" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="604" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="605" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="606" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="607" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="608" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="609" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="610" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="611" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="612" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="613" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="614" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="615" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="616" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="617" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="618" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="619" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="620" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="621" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="622" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="623" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="624" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="625" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="626" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="627" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="628" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="629" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="630" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="631" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="632" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="633" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="634" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="635" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="636" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="637" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="638" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="639" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="640" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="641" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="642" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="643" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="644" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="645" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="646" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="647" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="648" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="649" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="650" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="651" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="652" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="653" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="654" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="655" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="656" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="657" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="658" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="659" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="660" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="661" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="662" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="663" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="664" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="665" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="666" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="667" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="668" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="669" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="670" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="671" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="672" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="673" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="674" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="675" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="676" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="677" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="678" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="679" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="680" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="681" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="682" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="683" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="684" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="685" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="686" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="687" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="688" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="689" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="690" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="691" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="692" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="693" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="694" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="695" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="696" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="697" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="698" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="699" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="700" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="701" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="702" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="703" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="704" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="705" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="706" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="707" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="708" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="709" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="710" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="711" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="712" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="713" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="714" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="715" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="716" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="717" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="718" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="719" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="720" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="721" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="722" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="723" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="724" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="725" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="726" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="727" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="728" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="729" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="730" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="731" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="732" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="733" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="734" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="735" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="736" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="737" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="738" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="739" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="740" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="741" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="742" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="743" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="744" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="745" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="746" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="747" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="748" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="749" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="750" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="751" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="752" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="753" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="754" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="755" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="756" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="757" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="758" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="759" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="760" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="761" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="762" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="763" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="764" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="765" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="766" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="767" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="768" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="769" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="770" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="771" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="772" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="773" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="774" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="775" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="776" ht="13" x14ac:dyDescent="0.3"/>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="AC16" s="17">
+        <f t="shared" si="1"/>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="AD16" s="17">
+        <f t="shared" si="1"/>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="AE16" s="17">
+        <f t="shared" si="1"/>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="AF16" s="17">
+        <f t="shared" si="1"/>
+        <v>187921.33254093802</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32">
+      <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="17">
+        <f t="shared" si="2"/>
+        <v>8859.1485340727922</v>
+      </c>
+      <c r="D17" s="17">
+        <f t="shared" si="2"/>
+        <v>8053.7713946116301</v>
+      </c>
+      <c r="E17" s="17">
+        <f t="shared" si="2"/>
+        <v>6765.1679714737684</v>
+      </c>
+      <c r="F17" s="17">
+        <f t="shared" si="2"/>
+        <v>6190.6656119914733</v>
+      </c>
+      <c r="G17" s="17">
+        <f t="shared" si="2"/>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="H17" s="17">
+        <f t="shared" si="3"/>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="I17" s="17">
+        <f t="shared" si="1"/>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="J17" s="17">
+        <f t="shared" si="1"/>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="K17" s="17">
+        <f t="shared" si="1"/>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="L17" s="17">
+        <f t="shared" si="1"/>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="M17" s="17">
+        <f t="shared" si="1"/>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="N17" s="17">
+        <f t="shared" si="1"/>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="O17" s="17">
+        <f t="shared" si="1"/>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="P17" s="17">
+        <f t="shared" si="1"/>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="Q17" s="17">
+        <f t="shared" si="1"/>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="R17" s="17">
+        <f t="shared" si="1"/>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="S17" s="17">
+        <f t="shared" si="1"/>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="T17" s="17">
+        <f t="shared" si="1"/>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="U17" s="17">
+        <f t="shared" si="1"/>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="V17" s="17">
+        <f t="shared" si="1"/>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="W17" s="17">
+        <f t="shared" si="1"/>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="X17" s="17">
+        <f t="shared" si="1"/>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="Y17" s="17">
+        <f t="shared" si="1"/>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="Z17" s="17">
+        <f t="shared" si="1"/>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="AA17" s="17">
+        <f t="shared" si="1"/>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="AB17" s="17">
+        <f t="shared" si="1"/>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="AC17" s="17">
+        <f t="shared" si="1"/>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="AD17" s="17">
+        <f t="shared" si="1"/>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="AE17" s="17">
+        <f t="shared" si="1"/>
+        <v>4118.1617731114129</v>
+      </c>
+      <c r="AF17" s="17">
+        <f t="shared" si="1"/>
+        <v>4118.1617731114129</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="17">
+        <f t="shared" si="2"/>
+        <v>16912.919928684423</v>
+      </c>
+      <c r="D18" s="17">
+        <f t="shared" si="2"/>
+        <v>14110.207483359576</v>
+      </c>
+      <c r="E18" s="17">
+        <f t="shared" si="2"/>
+        <v>10448.426089276154</v>
+      </c>
+      <c r="F18" s="17">
+        <f t="shared" si="2"/>
+        <v>10856.483839936476</v>
+      </c>
+      <c r="G18" s="17">
+        <f t="shared" si="2"/>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="H18" s="17">
+        <f t="shared" si="3"/>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="I18" s="17">
+        <f t="shared" si="1"/>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="J18" s="17">
+        <f t="shared" si="1"/>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="K18" s="17">
+        <f t="shared" si="1"/>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="L18" s="17">
+        <f t="shared" si="1"/>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="M18" s="17">
+        <f t="shared" si="1"/>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="N18" s="17">
+        <f t="shared" si="1"/>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="O18" s="17">
+        <f t="shared" si="1"/>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="P18" s="17">
+        <f t="shared" si="1"/>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="Q18" s="17">
+        <f t="shared" si="1"/>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="R18" s="17">
+        <f t="shared" si="1"/>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="S18" s="17">
+        <f t="shared" si="1"/>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="T18" s="17">
+        <f t="shared" si="1"/>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="U18" s="17">
+        <f t="shared" si="1"/>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="V18" s="17">
+        <f t="shared" si="1"/>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="W18" s="17">
+        <f t="shared" si="1"/>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="X18" s="17">
+        <f t="shared" si="1"/>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="Y18" s="17">
+        <f t="shared" si="1"/>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="Z18" s="17">
+        <f t="shared" si="1"/>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="AA18" s="17">
+        <f t="shared" si="1"/>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="AB18" s="17">
+        <f t="shared" si="1"/>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="AC18" s="17">
+        <f t="shared" si="1"/>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="AD18" s="17">
+        <f t="shared" si="1"/>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="AE18" s="17">
+        <f t="shared" si="1"/>
+        <v>10684.670050184763</v>
+      </c>
+      <c r="AF18" s="17">
+        <f t="shared" si="1"/>
+        <v>10684.670050184763</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet4">
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <sheetData/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet5">
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="25.1796875" customWidth="1"/>
-    <col min="2" max="2" width="53.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.08203125" customWidth="1"/>
+    <col min="2" max="2" width="14.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:31">
+      <c r="A1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B1">
+      <c r="B1" s="12">
         <v>2021</v>
       </c>
-      <c r="C1">
+      <c r="C1" s="12">
         <v>2022</v>
       </c>
-      <c r="D1">
+      <c r="D1" s="12">
         <v>2023</v>
       </c>
-      <c r="E1">
+      <c r="E1" s="12">
         <v>2024</v>
       </c>
-      <c r="F1">
+      <c r="F1" s="12">
         <v>2025</v>
       </c>
-      <c r="G1">
+      <c r="G1" s="12">
         <v>2026</v>
       </c>
-      <c r="H1">
+      <c r="H1" s="12">
         <v>2027</v>
       </c>
-      <c r="I1">
+      <c r="I1" s="12">
         <v>2028</v>
       </c>
-      <c r="J1">
+      <c r="J1" s="12">
         <v>2029</v>
       </c>
-      <c r="K1">
+      <c r="K1" s="12">
         <v>2030</v>
       </c>
-      <c r="L1">
+      <c r="L1" s="12">
         <v>2031</v>
       </c>
-      <c r="M1">
+      <c r="M1" s="12">
         <v>2032</v>
       </c>
-      <c r="N1">
+      <c r="N1" s="12">
         <v>2033</v>
       </c>
-      <c r="O1">
+      <c r="O1" s="12">
         <v>2034</v>
       </c>
-      <c r="P1">
+      <c r="P1" s="12">
         <v>2035</v>
       </c>
-      <c r="Q1">
+      <c r="Q1" s="12">
         <v>2036</v>
       </c>
-      <c r="R1">
+      <c r="R1" s="12">
         <v>2037</v>
       </c>
-      <c r="S1">
+      <c r="S1" s="12">
         <v>2038</v>
       </c>
-      <c r="T1">
+      <c r="T1" s="12">
         <v>2039</v>
       </c>
-      <c r="U1">
+      <c r="U1" s="12">
         <v>2040</v>
       </c>
-      <c r="V1">
+      <c r="V1" s="12">
         <v>2041</v>
       </c>
-      <c r="W1">
+      <c r="W1" s="12">
         <v>2042</v>
       </c>
-      <c r="X1">
+      <c r="X1" s="12">
         <v>2043</v>
       </c>
-      <c r="Y1">
+      <c r="Y1" s="12">
         <v>2044</v>
       </c>
-      <c r="Z1">
+      <c r="Z1" s="12">
         <v>2045</v>
       </c>
-      <c r="AA1">
+      <c r="AA1" s="12">
         <v>2046</v>
       </c>
-      <c r="AB1">
+      <c r="AB1" s="12">
         <v>2047</v>
       </c>
-      <c r="AC1">
+      <c r="AC1" s="12">
         <v>2048</v>
       </c>
-      <c r="AD1">
+      <c r="AD1" s="12">
         <v>2049</v>
       </c>
-      <c r="AE1">
+      <c r="AE1" s="12">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="2" spans="1:31">
+      <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="19">
-        <f>'Passenger Vehicle Calculations'!C46</f>
-        <v>3036.0333459787557</v>
-      </c>
-      <c r="C2" s="19">
-        <f>'Passenger Vehicle Calculations'!D46</f>
-        <v>2273.5314681335358</v>
-      </c>
-      <c r="D2" s="19">
-        <f>'Passenger Vehicle Calculations'!E46</f>
-        <v>2371.7262681335355</v>
-      </c>
-      <c r="E2" s="19">
-        <f>'Passenger Vehicle Calculations'!F46</f>
-        <v>2329.8343100151742</v>
-      </c>
-      <c r="F2" s="19">
-        <f>'Passenger Vehicle Calculations'!G46</f>
-        <v>1671.1026100151744</v>
-      </c>
-      <c r="G2" s="19">
-        <f>'Passenger Vehicle Calculations'!H46</f>
-        <v>1625.6076100151745</v>
-      </c>
-      <c r="H2" s="19">
-        <f>'Passenger Vehicle Calculations'!I46</f>
-        <v>1591.1151100151747</v>
-      </c>
-      <c r="I2" s="19">
-        <f>'Passenger Vehicle Calculations'!J46</f>
-        <v>1593.1401100151747</v>
-      </c>
-      <c r="J2" s="19">
-        <f>'Passenger Vehicle Calculations'!K46</f>
-        <v>1599.8726100151744</v>
-      </c>
-      <c r="K2" s="19">
-        <f>'Passenger Vehicle Calculations'!L46</f>
-        <v>1658.1326100151746</v>
-      </c>
-      <c r="L2" s="19">
-        <f>'Passenger Vehicle Calculations'!M46</f>
-        <v>1713.9176100151744</v>
-      </c>
-      <c r="M2" s="19">
-        <f>'Passenger Vehicle Calculations'!N46</f>
-        <v>1724.7001100151747</v>
-      </c>
-      <c r="N2" s="19">
-        <f>'Passenger Vehicle Calculations'!O46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="O2" s="19">
-        <f>'Passenger Vehicle Calculations'!P46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="P2" s="19">
-        <f>'Passenger Vehicle Calculations'!Q46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Q2" s="19">
-        <f>'Passenger Vehicle Calculations'!R46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="R2" s="19">
-        <f>'Passenger Vehicle Calculations'!S46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="S2" s="19">
-        <f>'Passenger Vehicle Calculations'!T46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="T2" s="19">
-        <f>'Passenger Vehicle Calculations'!U46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="U2" s="19">
-        <f>'Passenger Vehicle Calculations'!V46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="V2" s="19">
-        <f>'Passenger Vehicle Calculations'!W46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="W2" s="19">
-        <f>'Passenger Vehicle Calculations'!X46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="X2" s="19">
-        <f>'Passenger Vehicle Calculations'!Y46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Y2" s="19">
-        <f>'Passenger Vehicle Calculations'!Z46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Z2" s="19">
-        <f>'Passenger Vehicle Calculations'!AA46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AA2" s="19">
-        <f>'Passenger Vehicle Calculations'!AB46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AB2" s="19">
-        <f>'Passenger Vehicle Calculations'!AC46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AC2" s="19">
-        <f>'Passenger Vehicle Calculations'!AD46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AD2" s="19">
-        <f>'Passenger Vehicle Calculations'!AE46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AE2" s="19">
-        <f>'Passenger Vehicle Calculations'!AF46</f>
-        <v>568.32511001517457</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="B2" s="13">
+        <f>'Passenger Vehicle Calculations'!B15</f>
+        <v>5369.1809297410864</v>
+      </c>
+      <c r="C2" s="13">
+        <f>'Passenger Vehicle Calculations'!C15</f>
+        <v>4832.2628367669777</v>
+      </c>
+      <c r="D2" s="13">
+        <f>'Passenger Vehicle Calculations'!D15</f>
+        <v>4617.4955995773344</v>
+      </c>
+      <c r="E2" s="13">
+        <f>'Passenger Vehicle Calculations'!E15</f>
+        <v>4295.3447437928689</v>
+      </c>
+      <c r="F2" s="13">
+        <f>'Passenger Vehicle Calculations'!F15</f>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="G2" s="13">
+        <f>'Passenger Vehicle Calculations'!G15</f>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="H2" s="13">
+        <f>'Passenger Vehicle Calculations'!H15</f>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="I2" s="13">
+        <f>'Passenger Vehicle Calculations'!I15</f>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="J2" s="13">
+        <f>'Passenger Vehicle Calculations'!J15</f>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="K2" s="13">
+        <f>'Passenger Vehicle Calculations'!K15</f>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="L2" s="13">
+        <f>'Passenger Vehicle Calculations'!L15</f>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="M2" s="13">
+        <f>'Passenger Vehicle Calculations'!M15</f>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="N2" s="13">
+        <f>'Passenger Vehicle Calculations'!N15</f>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="O2" s="13">
+        <f>'Passenger Vehicle Calculations'!O15</f>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="P2" s="13">
+        <f>'Passenger Vehicle Calculations'!P15</f>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="Q2" s="13">
+        <f>'Passenger Vehicle Calculations'!Q15</f>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="R2" s="13">
+        <f>'Passenger Vehicle Calculations'!R15</f>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="S2" s="13">
+        <f>'Passenger Vehicle Calculations'!S15</f>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="T2" s="13">
+        <f>'Passenger Vehicle Calculations'!T15</f>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="U2" s="13">
+        <f>'Passenger Vehicle Calculations'!U15</f>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="V2" s="13">
+        <f>'Passenger Vehicle Calculations'!V15</f>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="W2" s="13">
+        <f>'Passenger Vehicle Calculations'!W15</f>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="X2" s="13">
+        <f>'Passenger Vehicle Calculations'!X15</f>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="Y2" s="13">
+        <f>'Passenger Vehicle Calculations'!Y15</f>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="Z2" s="13">
+        <f>'Passenger Vehicle Calculations'!Z15</f>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="AA2" s="13">
+        <f>'Passenger Vehicle Calculations'!AA15</f>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="AB2" s="13">
+        <f>'Passenger Vehicle Calculations'!AB15</f>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="AC2" s="13">
+        <f>'Passenger Vehicle Calculations'!AC15</f>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="AD2" s="13">
+        <f>'Passenger Vehicle Calculations'!AD15</f>
+        <v>3436.2757950342957</v>
+      </c>
+      <c r="AE2" s="13">
+        <f>'Passenger Vehicle Calculations'!AE15</f>
+        <v>3436.2757950342957</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31">
+      <c r="A3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="19">
-        <v>0</v>
-      </c>
-      <c r="C3" s="19">
-        <v>0</v>
-      </c>
-      <c r="D3" s="19">
-        <v>0</v>
-      </c>
-      <c r="E3" s="19">
-        <v>0</v>
-      </c>
-      <c r="F3" s="19">
-        <v>0</v>
-      </c>
-      <c r="G3" s="19">
-        <v>0</v>
-      </c>
-      <c r="H3" s="19">
-        <v>0</v>
-      </c>
-      <c r="I3" s="19">
-        <v>0</v>
-      </c>
-      <c r="J3" s="19">
-        <v>0</v>
-      </c>
-      <c r="K3" s="19">
-        <v>0</v>
-      </c>
-      <c r="L3" s="19">
-        <v>0</v>
-      </c>
-      <c r="M3" s="19">
-        <v>0</v>
-      </c>
-      <c r="N3" s="19">
-        <v>0</v>
-      </c>
-      <c r="O3" s="19">
-        <v>0</v>
-      </c>
-      <c r="P3" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="19">
-        <v>0</v>
-      </c>
-      <c r="R3" s="19">
-        <v>0</v>
-      </c>
-      <c r="S3" s="19">
-        <v>0</v>
-      </c>
-      <c r="T3" s="19">
-        <v>0</v>
-      </c>
-      <c r="U3" s="19">
-        <v>0</v>
-      </c>
-      <c r="V3" s="19">
-        <v>0</v>
-      </c>
-      <c r="W3" s="19">
-        <v>0</v>
-      </c>
-      <c r="X3" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="B3" s="13">
+        <v>0</v>
+      </c>
+      <c r="C3" s="13">
+        <v>0</v>
+      </c>
+      <c r="D3" s="13">
+        <v>0</v>
+      </c>
+      <c r="E3" s="13">
+        <v>0</v>
+      </c>
+      <c r="F3" s="13">
+        <v>0</v>
+      </c>
+      <c r="G3" s="13">
+        <v>0</v>
+      </c>
+      <c r="H3" s="13">
+        <v>0</v>
+      </c>
+      <c r="I3" s="13">
+        <v>0</v>
+      </c>
+      <c r="J3" s="13">
+        <v>0</v>
+      </c>
+      <c r="K3" s="13">
+        <v>0</v>
+      </c>
+      <c r="L3" s="13">
+        <v>0</v>
+      </c>
+      <c r="M3" s="13">
+        <v>0</v>
+      </c>
+      <c r="N3" s="13">
+        <v>0</v>
+      </c>
+      <c r="O3" s="13">
+        <v>0</v>
+      </c>
+      <c r="P3" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="13">
+        <v>0</v>
+      </c>
+      <c r="R3" s="13">
+        <v>0</v>
+      </c>
+      <c r="S3" s="13">
+        <v>0</v>
+      </c>
+      <c r="T3" s="13">
+        <v>0</v>
+      </c>
+      <c r="U3" s="13">
+        <v>0</v>
+      </c>
+      <c r="V3" s="13">
+        <v>0</v>
+      </c>
+      <c r="W3" s="13">
+        <v>0</v>
+      </c>
+      <c r="X3" s="13">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31">
+      <c r="A4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="19">
-        <v>0</v>
-      </c>
-      <c r="C4" s="19">
-        <v>0</v>
-      </c>
-      <c r="D4" s="19">
-        <v>0</v>
-      </c>
-      <c r="E4" s="19">
-        <v>0</v>
-      </c>
-      <c r="F4" s="19">
-        <v>0</v>
-      </c>
-      <c r="G4" s="19">
-        <v>0</v>
-      </c>
-      <c r="H4" s="19">
-        <v>0</v>
-      </c>
-      <c r="I4" s="19">
-        <v>0</v>
-      </c>
-      <c r="J4" s="19">
-        <v>0</v>
-      </c>
-      <c r="K4" s="19">
-        <v>0</v>
-      </c>
-      <c r="L4" s="19">
-        <v>0</v>
-      </c>
-      <c r="M4" s="19">
-        <v>0</v>
-      </c>
-      <c r="N4" s="19">
-        <v>0</v>
-      </c>
-      <c r="O4" s="19">
-        <v>0</v>
-      </c>
-      <c r="P4" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="19">
-        <v>0</v>
-      </c>
-      <c r="R4" s="19">
-        <v>0</v>
-      </c>
-      <c r="S4" s="19">
-        <v>0</v>
-      </c>
-      <c r="T4" s="19">
-        <v>0</v>
-      </c>
-      <c r="U4" s="19">
-        <v>0</v>
-      </c>
-      <c r="V4" s="19">
-        <v>0</v>
-      </c>
-      <c r="W4" s="19">
-        <v>0</v>
-      </c>
-      <c r="X4" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="B4" s="13">
+        <v>0</v>
+      </c>
+      <c r="C4" s="13">
+        <v>0</v>
+      </c>
+      <c r="D4" s="13">
+        <v>0</v>
+      </c>
+      <c r="E4" s="13">
+        <v>0</v>
+      </c>
+      <c r="F4" s="13">
+        <v>0</v>
+      </c>
+      <c r="G4" s="13">
+        <v>0</v>
+      </c>
+      <c r="H4" s="13">
+        <v>0</v>
+      </c>
+      <c r="I4" s="13">
+        <v>0</v>
+      </c>
+      <c r="J4" s="13">
+        <v>0</v>
+      </c>
+      <c r="K4" s="13">
+        <v>0</v>
+      </c>
+      <c r="L4" s="13">
+        <v>0</v>
+      </c>
+      <c r="M4" s="13">
+        <v>0</v>
+      </c>
+      <c r="N4" s="13">
+        <v>0</v>
+      </c>
+      <c r="O4" s="13">
+        <v>0</v>
+      </c>
+      <c r="P4" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="13">
+        <v>0</v>
+      </c>
+      <c r="R4" s="13">
+        <v>0</v>
+      </c>
+      <c r="S4" s="13">
+        <v>0</v>
+      </c>
+      <c r="T4" s="13">
+        <v>0</v>
+      </c>
+      <c r="U4" s="13">
+        <v>0</v>
+      </c>
+      <c r="V4" s="13">
+        <v>0</v>
+      </c>
+      <c r="W4" s="13">
+        <v>0</v>
+      </c>
+      <c r="X4" s="13">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31">
+      <c r="A5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="19">
-        <v>0</v>
-      </c>
-      <c r="C5" s="19">
-        <v>0</v>
-      </c>
-      <c r="D5" s="19">
-        <v>0</v>
-      </c>
-      <c r="E5" s="19">
-        <v>0</v>
-      </c>
-      <c r="F5" s="19">
-        <v>0</v>
-      </c>
-      <c r="G5" s="19">
-        <v>0</v>
-      </c>
-      <c r="H5" s="19">
-        <v>0</v>
-      </c>
-      <c r="I5" s="19">
-        <v>0</v>
-      </c>
-      <c r="J5" s="19">
-        <v>0</v>
-      </c>
-      <c r="K5" s="19">
-        <v>0</v>
-      </c>
-      <c r="L5" s="19">
-        <v>0</v>
-      </c>
-      <c r="M5" s="19">
-        <v>0</v>
-      </c>
-      <c r="N5" s="19">
-        <v>0</v>
-      </c>
-      <c r="O5" s="19">
-        <v>0</v>
-      </c>
-      <c r="P5" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="19">
-        <v>0</v>
-      </c>
-      <c r="R5" s="19">
-        <v>0</v>
-      </c>
-      <c r="S5" s="19">
-        <v>0</v>
-      </c>
-      <c r="T5" s="19">
-        <v>0</v>
-      </c>
-      <c r="U5" s="19">
-        <v>0</v>
-      </c>
-      <c r="V5" s="19">
-        <v>0</v>
-      </c>
-      <c r="W5" s="19">
-        <v>0</v>
-      </c>
-      <c r="X5" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="B5" s="13">
+        <v>0</v>
+      </c>
+      <c r="C5" s="13">
+        <v>0</v>
+      </c>
+      <c r="D5" s="13">
+        <v>0</v>
+      </c>
+      <c r="E5" s="13">
+        <v>0</v>
+      </c>
+      <c r="F5" s="13">
+        <v>0</v>
+      </c>
+      <c r="G5" s="13">
+        <v>0</v>
+      </c>
+      <c r="H5" s="13">
+        <v>0</v>
+      </c>
+      <c r="I5" s="13">
+        <v>0</v>
+      </c>
+      <c r="J5" s="13">
+        <v>0</v>
+      </c>
+      <c r="K5" s="13">
+        <v>0</v>
+      </c>
+      <c r="L5" s="13">
+        <v>0</v>
+      </c>
+      <c r="M5" s="13">
+        <v>0</v>
+      </c>
+      <c r="N5" s="13">
+        <v>0</v>
+      </c>
+      <c r="O5" s="13">
+        <v>0</v>
+      </c>
+      <c r="P5" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="13">
+        <v>0</v>
+      </c>
+      <c r="R5" s="13">
+        <v>0</v>
+      </c>
+      <c r="S5" s="13">
+        <v>0</v>
+      </c>
+      <c r="T5" s="13">
+        <v>0</v>
+      </c>
+      <c r="U5" s="13">
+        <v>0</v>
+      </c>
+      <c r="V5" s="13">
+        <v>0</v>
+      </c>
+      <c r="W5" s="13">
+        <v>0</v>
+      </c>
+      <c r="X5" s="13">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31">
+      <c r="A6" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="19">
-        <f>'Passenger Vehicle Calculations'!C47</f>
-        <v>7252.8733459787563</v>
-      </c>
-      <c r="C6" s="19">
-        <f>'Passenger Vehicle Calculations'!D47</f>
-        <v>4193.501468133536</v>
-      </c>
-      <c r="D6" s="19">
-        <f>'Passenger Vehicle Calculations'!E47</f>
-        <v>2371.7262681335355</v>
-      </c>
-      <c r="E6" s="19">
-        <f>'Passenger Vehicle Calculations'!F47</f>
-        <v>2329.8343100151742</v>
-      </c>
-      <c r="F6" s="19">
-        <f>'Passenger Vehicle Calculations'!G47</f>
-        <v>1671.1026100151744</v>
-      </c>
-      <c r="G6" s="19">
-        <f>'Passenger Vehicle Calculations'!H47</f>
-        <v>1625.6076100151745</v>
-      </c>
-      <c r="H6" s="19">
-        <f>'Passenger Vehicle Calculations'!I47</f>
-        <v>1591.1151100151747</v>
-      </c>
-      <c r="I6" s="19">
-        <f>'Passenger Vehicle Calculations'!J47</f>
-        <v>1593.1401100151747</v>
-      </c>
-      <c r="J6" s="19">
-        <f>'Passenger Vehicle Calculations'!K47</f>
-        <v>1599.8726100151744</v>
-      </c>
-      <c r="K6" s="19">
-        <f>'Passenger Vehicle Calculations'!L47</f>
-        <v>1658.1326100151746</v>
-      </c>
-      <c r="L6" s="19">
-        <f>'Passenger Vehicle Calculations'!M47</f>
-        <v>1713.9176100151744</v>
-      </c>
-      <c r="M6" s="19">
-        <f>'Passenger Vehicle Calculations'!N47</f>
-        <v>1724.7001100151747</v>
-      </c>
-      <c r="N6" s="19">
-        <f>'Passenger Vehicle Calculations'!O47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="O6" s="19">
-        <f>'Passenger Vehicle Calculations'!P47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="P6" s="19">
-        <f>'Passenger Vehicle Calculations'!Q47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Q6" s="19">
-        <f>'Passenger Vehicle Calculations'!R47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="R6" s="19">
-        <f>'Passenger Vehicle Calculations'!S47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="S6" s="19">
-        <f>'Passenger Vehicle Calculations'!T47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="T6" s="19">
-        <f>'Passenger Vehicle Calculations'!U47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="U6" s="19">
-        <f>'Passenger Vehicle Calculations'!V47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="V6" s="19">
-        <f>'Passenger Vehicle Calculations'!W47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="W6" s="19">
-        <f>'Passenger Vehicle Calculations'!X47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="X6" s="19">
-        <f>'Passenger Vehicle Calculations'!Y47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Y6" s="19">
-        <f>'Passenger Vehicle Calculations'!Z47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Z6" s="19">
-        <f>'Passenger Vehicle Calculations'!AA47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AA6" s="19">
-        <f>'Passenger Vehicle Calculations'!AB47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AB6" s="19">
-        <f>'Passenger Vehicle Calculations'!AC47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AC6" s="19">
-        <f>'Passenger Vehicle Calculations'!AD47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AD6" s="19">
-        <f>'Passenger Vehicle Calculations'!AE47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AE6" s="19">
-        <f>'Passenger Vehicle Calculations'!AF47</f>
-        <v>568.32511001517457</v>
-      </c>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="B6" s="13">
+        <f>'Passenger Vehicle Calculations'!B16</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="13">
+        <f>'Passenger Vehicle Calculations'!C16</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="13">
+        <f>'Passenger Vehicle Calculations'!D16</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="13">
+        <f>'Passenger Vehicle Calculations'!E16</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="13">
+        <f>'Passenger Vehicle Calculations'!F16</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="13">
+        <f>'Passenger Vehicle Calculations'!G16</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="13">
+        <f>'Passenger Vehicle Calculations'!H16</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="13">
+        <f>'Passenger Vehicle Calculations'!I16</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="13">
+        <f>'Passenger Vehicle Calculations'!J16</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="13">
+        <f>'Passenger Vehicle Calculations'!K16</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="13">
+        <f>'Passenger Vehicle Calculations'!L16</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="13">
+        <f>'Passenger Vehicle Calculations'!M16</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="13">
+        <f>'Passenger Vehicle Calculations'!N16</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="13">
+        <f>'Passenger Vehicle Calculations'!O16</f>
+        <v>0</v>
+      </c>
+      <c r="P6" s="13">
+        <f>'Passenger Vehicle Calculations'!P16</f>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="13">
+        <f>'Passenger Vehicle Calculations'!Q16</f>
+        <v>0</v>
+      </c>
+      <c r="R6" s="13">
+        <f>'Passenger Vehicle Calculations'!R16</f>
+        <v>0</v>
+      </c>
+      <c r="S6" s="13">
+        <f>'Passenger Vehicle Calculations'!S16</f>
+        <v>0</v>
+      </c>
+      <c r="T6" s="13">
+        <f>'Passenger Vehicle Calculations'!T16</f>
+        <v>0</v>
+      </c>
+      <c r="U6" s="13">
+        <f>'Passenger Vehicle Calculations'!U16</f>
+        <v>0</v>
+      </c>
+      <c r="V6" s="13">
+        <f>'Passenger Vehicle Calculations'!V16</f>
+        <v>0</v>
+      </c>
+      <c r="W6" s="13">
+        <f>'Passenger Vehicle Calculations'!W16</f>
+        <v>0</v>
+      </c>
+      <c r="X6" s="13">
+        <f>'Passenger Vehicle Calculations'!X16</f>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="13">
+        <f>'Passenger Vehicle Calculations'!Y16</f>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="13">
+        <f>'Passenger Vehicle Calculations'!Z16</f>
+        <v>0</v>
+      </c>
+      <c r="AA6" s="13">
+        <f>'Passenger Vehicle Calculations'!AA16</f>
+        <v>0</v>
+      </c>
+      <c r="AB6" s="13">
+        <f>'Passenger Vehicle Calculations'!AB16</f>
+        <v>0</v>
+      </c>
+      <c r="AC6" s="13">
+        <f>'Passenger Vehicle Calculations'!AC16</f>
+        <v>0</v>
+      </c>
+      <c r="AD6" s="13">
+        <f>'Passenger Vehicle Calculations'!AD16</f>
+        <v>0</v>
+      </c>
+      <c r="AE6" s="13">
+        <f>'Passenger Vehicle Calculations'!AE16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31">
+      <c r="A7" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="19">
-        <v>0</v>
-      </c>
-      <c r="C7" s="19">
-        <v>0</v>
-      </c>
-      <c r="D7" s="19">
-        <v>0</v>
-      </c>
-      <c r="E7" s="19">
-        <v>0</v>
-      </c>
-      <c r="F7" s="19">
-        <v>0</v>
-      </c>
-      <c r="G7" s="19">
-        <v>0</v>
-      </c>
-      <c r="H7" s="19">
-        <v>0</v>
-      </c>
-      <c r="I7" s="19">
-        <v>0</v>
-      </c>
-      <c r="J7" s="19">
-        <v>0</v>
-      </c>
-      <c r="K7" s="19">
-        <v>0</v>
-      </c>
-      <c r="L7" s="19">
-        <v>0</v>
-      </c>
-      <c r="M7" s="19">
-        <v>0</v>
-      </c>
-      <c r="N7" s="19">
-        <v>0</v>
-      </c>
-      <c r="O7" s="19">
-        <v>0</v>
-      </c>
-      <c r="P7" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="19">
-        <v>0</v>
-      </c>
-      <c r="R7" s="19">
-        <v>0</v>
-      </c>
-      <c r="S7" s="19">
-        <v>0</v>
-      </c>
-      <c r="T7" s="19">
-        <v>0</v>
-      </c>
-      <c r="U7" s="19">
-        <v>0</v>
-      </c>
-      <c r="V7" s="19">
-        <v>0</v>
-      </c>
-      <c r="W7" s="19">
-        <v>0</v>
-      </c>
-      <c r="X7" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="B7" s="13">
+        <v>0</v>
+      </c>
+      <c r="C7" s="13">
+        <v>0</v>
+      </c>
+      <c r="D7" s="13">
+        <v>0</v>
+      </c>
+      <c r="E7" s="13">
+        <v>0</v>
+      </c>
+      <c r="F7" s="13">
+        <v>0</v>
+      </c>
+      <c r="G7" s="13">
+        <v>0</v>
+      </c>
+      <c r="H7" s="13">
+        <v>0</v>
+      </c>
+      <c r="I7" s="13">
+        <v>0</v>
+      </c>
+      <c r="J7" s="13">
+        <v>0</v>
+      </c>
+      <c r="K7" s="13">
+        <v>0</v>
+      </c>
+      <c r="L7" s="13">
+        <v>0</v>
+      </c>
+      <c r="M7" s="13">
+        <v>0</v>
+      </c>
+      <c r="N7" s="13">
+        <v>0</v>
+      </c>
+      <c r="O7" s="13">
+        <v>0</v>
+      </c>
+      <c r="P7" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="13">
+        <v>0</v>
+      </c>
+      <c r="R7" s="13">
+        <v>0</v>
+      </c>
+      <c r="S7" s="13">
+        <v>0</v>
+      </c>
+      <c r="T7" s="13">
+        <v>0</v>
+      </c>
+      <c r="U7" s="13">
+        <v>0</v>
+      </c>
+      <c r="V7" s="13">
+        <v>0</v>
+      </c>
+      <c r="W7" s="13">
+        <v>0</v>
+      </c>
+      <c r="X7" s="13">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31">
+      <c r="A8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="19">
-        <v>0</v>
-      </c>
-      <c r="C8" s="19">
-        <v>0</v>
-      </c>
-      <c r="D8" s="19">
-        <f>D2</f>
-        <v>2371.7262681335355</v>
-      </c>
-      <c r="E8" s="19">
-        <f t="shared" ref="E8:AE8" si="0">E2</f>
-        <v>2329.8343100151742</v>
-      </c>
-      <c r="F8" s="19">
-        <f t="shared" si="0"/>
-        <v>1671.1026100151744</v>
-      </c>
-      <c r="G8" s="19">
-        <f t="shared" si="0"/>
-        <v>1625.6076100151745</v>
-      </c>
-      <c r="H8" s="19">
-        <f t="shared" si="0"/>
-        <v>1591.1151100151747</v>
-      </c>
-      <c r="I8" s="19">
-        <f t="shared" si="0"/>
-        <v>1593.1401100151747</v>
-      </c>
-      <c r="J8" s="19">
-        <f t="shared" si="0"/>
-        <v>1599.8726100151744</v>
-      </c>
-      <c r="K8" s="19">
-        <f t="shared" si="0"/>
-        <v>1658.1326100151746</v>
-      </c>
-      <c r="L8" s="19">
-        <f t="shared" si="0"/>
-        <v>1713.9176100151744</v>
-      </c>
-      <c r="M8" s="19">
-        <f t="shared" si="0"/>
-        <v>1724.7001100151747</v>
-      </c>
-      <c r="N8" s="19">
-        <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="O8" s="19">
-        <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="P8" s="19">
-        <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Q8" s="19">
-        <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="R8" s="19">
-        <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="S8" s="19">
-        <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="T8" s="19">
-        <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="U8" s="19">
-        <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="V8" s="19">
-        <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="W8" s="19">
-        <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="X8" s="19">
-        <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Y8" s="19">
-        <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Z8" s="19">
-        <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AA8" s="19">
-        <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AB8" s="19">
-        <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AC8" s="19">
-        <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AD8" s="19">
-        <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AE8" s="19">
-        <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
+      <c r="B8" s="13">
+        <f>'Passenger Vehicle Calculations'!B17</f>
+        <v>12080.657091917445</v>
+      </c>
+      <c r="C8" s="13">
+        <f>'Passenger Vehicle Calculations'!C17</f>
+        <v>17449.838021658532</v>
+      </c>
+      <c r="D8" s="13">
+        <f>'Passenger Vehicle Calculations'!D17</f>
+        <v>17449.838021658532</v>
+      </c>
+      <c r="E8" s="13">
+        <f>'Passenger Vehicle Calculations'!E17</f>
+        <v>17449.838021658532</v>
+      </c>
+      <c r="F8" s="13">
+        <f>'Passenger Vehicle Calculations'!F17</f>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="G8" s="13">
+        <f>'Passenger Vehicle Calculations'!G17</f>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="H8" s="13">
+        <f>'Passenger Vehicle Calculations'!H17</f>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="I8" s="13">
+        <f>'Passenger Vehicle Calculations'!I17</f>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="J8" s="13">
+        <f>'Passenger Vehicle Calculations'!J17</f>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="K8" s="13">
+        <f>'Passenger Vehicle Calculations'!K17</f>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="L8" s="13">
+        <f>'Passenger Vehicle Calculations'!L17</f>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="M8" s="13">
+        <f>'Passenger Vehicle Calculations'!M17</f>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="N8" s="13">
+        <f>'Passenger Vehicle Calculations'!N17</f>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="O8" s="13">
+        <f>'Passenger Vehicle Calculations'!O17</f>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="P8" s="13">
+        <f>'Passenger Vehicle Calculations'!P17</f>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="Q8" s="13">
+        <f>'Passenger Vehicle Calculations'!Q17</f>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="R8" s="13">
+        <f>'Passenger Vehicle Calculations'!R17</f>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="S8" s="13">
+        <f>'Passenger Vehicle Calculations'!S17</f>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="T8" s="13">
+        <f>'Passenger Vehicle Calculations'!T17</f>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="U8" s="13">
+        <f>'Passenger Vehicle Calculations'!U17</f>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="V8" s="13">
+        <f>'Passenger Vehicle Calculations'!V17</f>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="W8" s="13">
+        <f>'Passenger Vehicle Calculations'!W17</f>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="X8" s="13">
+        <f>'Passenger Vehicle Calculations'!X17</f>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="Y8" s="13">
+        <f>'Passenger Vehicle Calculations'!Y17</f>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="Z8" s="13">
+        <f>'Passenger Vehicle Calculations'!Z17</f>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="AA8" s="13">
+        <f>'Passenger Vehicle Calculations'!AA17</f>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="AB8" s="13">
+        <f>'Passenger Vehicle Calculations'!AB17</f>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="AC8" s="13">
+        <f>'Passenger Vehicle Calculations'!AC17</f>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="AD8" s="13">
+        <f>'Passenger Vehicle Calculations'!AD17</f>
+        <v>15839.083742736204</v>
+      </c>
+      <c r="AE8" s="13">
+        <f>'Passenger Vehicle Calculations'!AE17</f>
+        <v>15839.083742736204</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -11142,16 +8989,16 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55534DDE-5D7D-440E-9F2D-C8BE7EE78DD9}">
-  <sheetPr>
+  <sheetPr codeName="Sheet6">
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -11246,112 +9093,132 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <f>'Commercial Vehicles'!$B$7</f>
-        <v>27004</v>
-      </c>
-      <c r="E2">
-        <f>'Commercial Vehicles'!$B$7</f>
-        <v>27004</v>
-      </c>
-      <c r="F2">
-        <f>'Commercial Vehicles'!$B$7</f>
-        <v>27004</v>
-      </c>
-      <c r="G2">
-        <f>'Commercial Vehicles'!$B$7</f>
-        <v>27004</v>
-      </c>
-      <c r="H2">
-        <f>'Commercial Vehicles'!$B$7</f>
-        <v>27004</v>
-      </c>
-      <c r="I2">
-        <f>'Commercial Vehicles'!$B$7</f>
-        <v>27004</v>
-      </c>
-      <c r="J2">
-        <f>'Commercial Vehicles'!$B$7</f>
-        <v>27004</v>
-      </c>
-      <c r="K2">
-        <f>'Commercial Vehicles'!$B$7</f>
-        <v>27004</v>
-      </c>
-      <c r="L2">
-        <f>'Commercial Vehicles'!$B$7</f>
-        <v>27004</v>
-      </c>
-      <c r="M2">
-        <f>'Commercial Vehicles'!$B$7</f>
-        <v>27004</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="B2" s="17">
+        <f>'승합차 및 화물차'!C15</f>
+        <v>180189.71200211087</v>
+      </c>
+      <c r="C2" s="17">
+        <f>'승합차 및 화물차'!D15</f>
+        <v>157778.75080137159</v>
+      </c>
+      <c r="D2" s="17">
+        <f>'승합차 및 화물차'!E15</f>
+        <v>63893.253063918928</v>
+      </c>
+      <c r="E2" s="17">
+        <f>'승합차 및 화물차'!F15</f>
+        <v>91276.075805598477</v>
+      </c>
+      <c r="F2" s="17">
+        <f>'승합차 및 화물차'!G15</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="G2" s="17">
+        <f>'승합차 및 화물차'!H15</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="H2" s="17">
+        <f>'승합차 및 화물차'!I15</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="I2" s="17">
+        <f>'승합차 및 화물차'!J15</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="J2" s="17">
+        <f>'승합차 및 화물차'!K15</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="K2" s="17">
+        <f>'승합차 및 화물차'!L15</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="L2" s="17">
+        <f>'승합차 및 화물차'!M15</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="M2" s="17">
+        <f>'승합차 및 화물차'!N15</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="N2" s="17">
+        <f>'승합차 및 화물차'!O15</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="O2" s="17">
+        <f>'승합차 및 화물차'!P15</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="P2" s="17">
+        <f>'승합차 및 화물차'!Q15</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="Q2" s="17">
+        <f>'승합차 및 화물차'!R15</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="R2" s="17">
+        <f>'승합차 및 화물차'!S15</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="S2" s="17">
+        <f>'승합차 및 화물차'!T15</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="T2" s="17">
+        <f>'승합차 및 화물차'!U15</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="U2" s="17">
+        <f>'승합차 및 화물차'!V15</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="V2" s="17">
+        <f>'승합차 및 화물차'!W15</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="W2" s="17">
+        <f>'승합차 및 화물차'!X15</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="X2" s="17">
+        <f>'승합차 및 화물차'!Y15</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="Y2" s="17">
+        <f>'승합차 및 화물차'!Z15</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="Z2" s="17">
+        <f>'승합차 및 화물차'!AA15</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="AA2" s="17">
+        <f>'승합차 및 화물차'!AB15</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="AB2" s="17">
+        <f>'승합차 및 화물차'!AC15</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="AC2" s="17">
+        <f>'승합차 및 화물차'!AD15</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="AD2" s="17">
+        <f>'승합차 및 화물차'!AE15</f>
+        <v>106374.21258003041</v>
+      </c>
+      <c r="AE2" s="17">
+        <f>'승합차 및 화물차'!AF15</f>
+        <v>106374.21258003041</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -11446,7 +9313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -11541,7 +9408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -11636,7 +9503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -11647,44 +9514,34 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <f>D2</f>
-        <v>27004</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <f t="shared" ref="E6:M6" si="0">E2</f>
-        <v>27004</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <f t="shared" si="0"/>
-        <v>27004</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <f t="shared" si="0"/>
-        <v>27004</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <f t="shared" si="0"/>
-        <v>27004</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <f t="shared" si="0"/>
-        <v>27004</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <f t="shared" si="0"/>
-        <v>27004</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <f t="shared" si="0"/>
-        <v>27004</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <f t="shared" si="0"/>
-        <v>27004</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <f t="shared" si="0"/>
-        <v>27004</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -11741,7 +9598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -11836,128 +9693,149 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <f>D2</f>
-        <v>27004</v>
-      </c>
-      <c r="E8">
-        <f t="shared" ref="E8:M8" si="1">E2</f>
-        <v>27004</v>
-      </c>
-      <c r="F8">
-        <f t="shared" si="1"/>
-        <v>27004</v>
-      </c>
-      <c r="G8">
-        <f t="shared" si="1"/>
-        <v>27004</v>
-      </c>
-      <c r="H8">
-        <f t="shared" si="1"/>
-        <v>27004</v>
-      </c>
-      <c r="I8">
-        <f t="shared" si="1"/>
-        <v>27004</v>
-      </c>
-      <c r="J8">
-        <f t="shared" si="1"/>
-        <v>27004</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="1"/>
-        <v>27004</v>
-      </c>
-      <c r="L8">
-        <f t="shared" si="1"/>
-        <v>27004</v>
-      </c>
-      <c r="M8">
-        <f t="shared" si="1"/>
-        <v>27004</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <v>0</v>
-      </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
+      <c r="B8" s="17">
+        <f>'승합차 및 화물차'!C16</f>
+        <v>80537.713946116302</v>
+      </c>
+      <c r="C8" s="17">
+        <f>'승합차 및 화물차'!D16</f>
+        <v>161075.4278922326</v>
+      </c>
+      <c r="D8" s="17">
+        <f>'승합차 및 화물차'!E16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="E8" s="17">
+        <f>'승합차 및 화물차'!F16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="F8" s="17">
+        <f>'승합차 및 화물차'!G16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="G8" s="17">
+        <f>'승합차 및 화물차'!H16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="H8" s="17">
+        <f>'승합차 및 화물차'!I16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="I8" s="17">
+        <f>'승합차 및 화물차'!J16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="J8" s="17">
+        <f>'승합차 및 화물차'!K16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="K8" s="17">
+        <f>'승합차 및 화물차'!L16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="L8" s="17">
+        <f>'승합차 및 화물차'!M16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="M8" s="17">
+        <f>'승합차 및 화물차'!N16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="N8" s="17">
+        <f>'승합차 및 화물차'!O16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="O8" s="17">
+        <f>'승합차 및 화물차'!P16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="P8" s="17">
+        <f>'승합차 및 화물차'!Q16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="Q8" s="17">
+        <f>'승합차 및 화물차'!R16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="R8" s="17">
+        <f>'승합차 및 화물차'!S16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="S8" s="17">
+        <f>'승합차 및 화물차'!T16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="T8" s="17">
+        <f>'승합차 및 화물차'!U16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="U8" s="17">
+        <f>'승합차 및 화물차'!V16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="V8" s="17">
+        <f>'승합차 및 화물차'!W16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="W8" s="17">
+        <f>'승합차 및 화물차'!X16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="X8" s="17">
+        <f>'승합차 및 화물차'!Y16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="Y8" s="17">
+        <f>'승합차 및 화물차'!Z16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="Z8" s="17">
+        <f>'승합차 및 화물차'!AA16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="AA8" s="17">
+        <f>'승합차 및 화물차'!AB16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="AB8" s="17">
+        <f>'승합차 및 화물차'!AC16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="AC8" s="17">
+        <f>'승합차 및 화물차'!AD16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="AD8" s="17">
+        <f>'승합차 및 화물차'!AE16</f>
+        <v>187921.33254093802</v>
+      </c>
+      <c r="AE8" s="17">
+        <f>'승합차 및 화물차'!AF16</f>
+        <v>187921.33254093802</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A1741F6-596C-4C6D-91F8-CA5AA118CF11}">
-  <sheetPr>
+  <sheetPr codeName="Sheet7">
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -12052,7 +9930,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -12147,7 +10025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -12242,7 +10120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -12337,7 +10215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -12432,7 +10310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -12527,7 +10405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -12622,7 +10500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -12718,22 +10596,23 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9A94405-868B-4452-B9AC-D6B63E4037BA}">
-  <sheetPr>
+  <sheetPr codeName="Sheet8">
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -12828,7 +10707,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -12923,7 +10802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -13018,7 +10897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -13113,7 +10992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -13208,7 +11087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -13303,7 +11182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -13398,7 +11277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -13494,22 +11373,23 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94E87FBF-8038-4912-A5A6-BE7241A5CAB0}">
-  <sheetPr>
+  <sheetPr codeName="Sheet9">
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -13604,7 +11484,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -13699,7 +11579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -13794,7 +11674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -13889,7 +11769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -13984,7 +11864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -14079,7 +11959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -14174,7 +12054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -14270,6 +12150,178 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C06AC8A-D68E-4783-830B-F8A6C3E09A8C}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27F23C23-7C9C-4450-A9B4-C8130737FEF9}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2860DEC-23A4-46FB-AC4F-A35AB80E4B05}"/>
 </file>